--- a/EFN_Modelv2.xlsx
+++ b/EFN_Modelv2.xlsx
@@ -19,7 +19,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="11">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="0&quot;A&quot;"/>
     <numFmt numFmtId="165" formatCode="0&quot;E&quot;"/>
     <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
@@ -30,7 +30,6 @@
     <numFmt numFmtId="171" formatCode="[&lt;=9999999]###\-####;###\-###\-####"/>
     <numFmt numFmtId="172" formatCode="0.0%"/>
     <numFmt numFmtId="173" formatCode="0.0\x"/>
-    <numFmt numFmtId="174" formatCode="0.0"/>
   </numFmts>
   <fonts count="37">
     <font>
@@ -999,8 +998,8 @@
     <xf numFmtId="167" fontId="24" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="21" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="169" fontId="18" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="174" fontId="10" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="10" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="169" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="167" fontId="14" fillId="6" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="14" fillId="6" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -6314,52 +6313,52 @@
         <v>250.255</v>
       </c>
       <c r="L76" s="342">
-        <f>L78*L17/L4</f>
-        <v>239.2286093993726</v>
+        <f>L78*'Revenue Build'!L41</f>
+        <v>265.1122240525096</v>
       </c>
       <c r="M76" s="342">
-        <f>M78*M17/M4</f>
-        <v>254.26057826293365</v>
+        <f>M78*'Revenue Build'!M41</f>
+        <v>273.43535640337484</v>
       </c>
       <c r="N76" s="342">
-        <f>N78*N17/N4</f>
-        <v>257.64979122204375</v>
+        <f>N78*'Revenue Build'!N41</f>
+        <v>269.90805439615684</v>
       </c>
       <c r="O76" s="342">
-        <f>N76</f>
-        <v>257.64979122204375</v>
+        <f>O78*'Revenue Build'!O41</f>
+        <v>269.90805439615684</v>
       </c>
       <c r="P76" s="342">
-        <f>P78*P17/P4</f>
-        <v>249.18981303597323</v>
+        <f>P78*'Revenue Build'!P41</f>
+        <v>270.1627788048918</v>
       </c>
       <c r="Q76" s="342">
-        <f>Q78*Q17/Q4</f>
-        <v>262.91708473433005</v>
+        <f>Q78*'Revenue Build'!Q41</f>
+        <v>284.6769537346952</v>
       </c>
       <c r="R76" s="342">
-        <f>R78*R17/R4</f>
-        <v>278.28795488191724</v>
+        <f>R78*'Revenue Build'!R41</f>
+        <v>292.5625155118958</v>
       </c>
       <c r="S76" s="342">
-        <f>S78*S17/S4</f>
-        <v>279.55726921297673</v>
+        <f>S78*'Revenue Build'!S41</f>
+        <v>288.4063090846482</v>
       </c>
       <c r="T76" s="342">
-        <f>S76</f>
-        <v>279.55726921297673</v>
+        <f>T78*'Revenue Build'!T41</f>
+        <v>288.4063090846483</v>
       </c>
       <c r="U76" s="342">
-        <f>U78*U17/U4</f>
-        <v>291.3277597567618</v>
+        <f>U78*'Revenue Build'!U41</f>
+        <v>308.1481319193533</v>
       </c>
       <c r="V76" s="342">
-        <f>V78*V17/V4</f>
-        <v>317.3180292884783</v>
+        <f>V78*'Revenue Build'!V41</f>
+        <v>325.9904626641905</v>
       </c>
       <c r="W76" s="342">
-        <f>W78*W17/W4</f>
-        <v>340.85564125637933</v>
+        <f>W78*'Revenue Build'!W41</f>
+        <v>342.5836100413311</v>
       </c>
     </row>
     <row r="77" outlineLevel="1" s="20">
@@ -6403,143 +6402,139 @@
       </c>
       <c r="L77" s="343">
         <f>L76</f>
-        <v>239.2286093993726</v>
+        <v>265.1122240525096</v>
       </c>
       <c r="M77" s="343">
         <f>M76</f>
-        <v>254.26057826293365</v>
+        <v>273.43535640337484</v>
       </c>
       <c r="N77" s="343">
         <f>N76</f>
-        <v>257.64979122204375</v>
+        <v>269.90805439615684</v>
       </c>
       <c r="O77" s="343">
         <f>O76</f>
-        <v>257.64979122204375</v>
+        <v>269.90805439615684</v>
       </c>
       <c r="P77" s="343">
         <f>P76</f>
-        <v>249.18981303597323</v>
+        <v>270.1627788048918</v>
       </c>
       <c r="Q77" s="343">
         <f>Q76</f>
-        <v>262.91708473433005</v>
+        <v>284.6769537346952</v>
       </c>
       <c r="R77" s="343">
         <f>R76</f>
-        <v>278.28795488191724</v>
+        <v>292.5625155118958</v>
       </c>
       <c r="S77" s="343">
         <f>S76</f>
-        <v>279.55726921297673</v>
+        <v>288.4063090846482</v>
       </c>
       <c r="T77" s="343">
         <f>T76</f>
-        <v>279.55726921297673</v>
+        <v>288.4063090846483</v>
       </c>
       <c r="U77" s="343">
         <f>U76</f>
-        <v>291.3277597567618</v>
+        <v>308.1481319193533</v>
       </c>
       <c r="V77" s="343">
         <f>V76</f>
-        <v>317.3180292884783</v>
+        <v>325.9904626641905</v>
       </c>
       <c r="W77" s="343">
         <f>W76</f>
-        <v>340.85564125637933</v>
+        <v>342.5836100413311</v>
       </c>
     </row>
     <row r="78" outlineLevel="1" ht="5.1" customHeight="1" s="20">
       <c r="B78" s="167" t="inlineStr">
         <is>
-          <t>Accounts receivable - days of revenue (DSO)</t>
+          <t>Accounts receivable - % of Net Earning Assets</t>
         </is>
       </c>
       <c r="C78" s="72" t="inlineStr">
         <is>
-          <t>days</t>
-        </is>
-      </c>
-      <c r="D78" s="344">
-        <f>D76/D17*D4</f>
-        <v>77.25820744237575</v>
+          <t>%</t>
+        </is>
       </c>
       <c r="E78" s="344">
-        <f>E76/E17*E4</f>
-        <v>68.03623524219354</v>
+        <f>E76/'Revenue Build'!E41</f>
+        <v>0.02730625831000724</v>
       </c>
       <c r="F78" s="344">
-        <f>F76/F17*F4</f>
-        <v>60.44117807096139</v>
+        <f>F76/'Revenue Build'!F41</f>
+        <v>0.02443438113764817</v>
       </c>
       <c r="G78" s="344">
-        <f>G76/G17*G4</f>
-        <v>77.94047430230393</v>
+        <f>G76/'Revenue Build'!G41</f>
+        <v>0.0299636979481108</v>
       </c>
       <c r="H78" s="344">
-        <f>H76/H17*H4</f>
-        <v>64.11113939749991</v>
+        <f>H76/'Revenue Build'!H41</f>
+        <v>0.0242889892706216</v>
       </c>
       <c r="I78" s="344">
-        <f>I76/I17*I4</f>
-        <v>71.94200808492037</v>
+        <f>I76/'Revenue Build'!I41</f>
+        <v>0.02767746967691475</v>
       </c>
       <c r="J78" s="344">
-        <f>J76/J17*J4</f>
-        <v>75.45938035107253</v>
+        <f>J76/'Revenue Build'!J41</f>
+        <v>0.02767746967691475</v>
       </c>
       <c r="K78" s="344">
-        <f>K76/K17*K4</f>
-        <v>69.6192769445715</v>
+        <f>K76/'Revenue Build'!K41</f>
+        <v>0.029652819520964567</v>
       </c>
       <c r="L78" s="345">
         <f>$K$78</f>
-        <v>69.6192769445715</v>
+        <v>0.029652819520964567</v>
       </c>
       <c r="M78" s="345">
         <f>$K$78</f>
-        <v>69.6192769445715</v>
+        <v>0.029652819520964567</v>
       </c>
       <c r="N78" s="345">
         <f>$K$78</f>
-        <v>69.6192769445715</v>
+        <v>0.029652819520964567</v>
       </c>
       <c r="O78" s="345">
-        <f>O76/O17*O4</f>
-        <v>71.64082579753891</v>
+        <f>$K$78</f>
+        <v>0.029652819520964567</v>
       </c>
       <c r="P78" s="345">
         <f>$K$78</f>
-        <v>69.6192769445715</v>
+        <v>0.029652819520964567</v>
       </c>
       <c r="Q78" s="345">
         <f>$K$78</f>
-        <v>69.6192769445715</v>
+        <v>0.029652819520964567</v>
       </c>
       <c r="R78" s="345">
         <f>$K$78</f>
-        <v>69.6192769445715</v>
+        <v>0.029652819520964567</v>
       </c>
       <c r="S78" s="345">
         <f>$K$78</f>
-        <v>69.6192769445715</v>
+        <v>0.029652819520964567</v>
       </c>
       <c r="T78" s="345">
-        <f>T76/T17*T4</f>
-        <v>72.36276668037138</v>
+        <f>$K$78</f>
+        <v>0.029652819520964567</v>
       </c>
       <c r="U78" s="345">
         <f>$K$78</f>
-        <v>69.6192769445715</v>
+        <v>0.029652819520964567</v>
       </c>
       <c r="V78" s="345">
         <f>$K$78</f>
-        <v>69.6192769445715</v>
+        <v>0.029652819520964567</v>
       </c>
       <c r="W78" s="345">
         <f>$K$78</f>
-        <v>69.6192769445715</v>
+        <v>0.029652819520964567</v>
       </c>
     </row>
     <row r="79" outlineLevel="1" s="20">
@@ -6594,52 +6589,52 @@
         <v>1102.559</v>
       </c>
       <c r="L80" s="342">
-        <f>L82*L17/L4</f>
-        <v>1053.9795662454812</v>
+        <f>L82*'Revenue Build'!L41</f>
+        <v>1168.016098136345</v>
       </c>
       <c r="M80" s="342">
-        <f>M82*M17/M4</f>
-        <v>1120.2065449601482</v>
+        <f>M82*'Revenue Build'!M41</f>
+        <v>1204.6856730964362</v>
       </c>
       <c r="N80" s="342">
-        <f>N82*N17/N4</f>
-        <v>1135.1385433257492</v>
+        <f>N82*'Revenue Build'!N41</f>
+        <v>1189.1452899920976</v>
       </c>
       <c r="O80" s="342">
-        <f>N80</f>
-        <v>1135.1385433257492</v>
+        <f>O82*'Revenue Build'!O41</f>
+        <v>1189.1452899920976</v>
       </c>
       <c r="P80" s="342">
-        <f>P82*P17/P4</f>
-        <v>1097.8660609023982</v>
+        <f>P82*'Revenue Build'!P41</f>
+        <v>1190.2675400545152</v>
       </c>
       <c r="Q80" s="342">
-        <f>Q82*Q17/Q4</f>
-        <v>1158.3448803324538</v>
+        <f>Q82*'Revenue Build'!Q41</f>
+        <v>1254.213252213829</v>
       </c>
       <c r="R80" s="342">
-        <f>R82*R17/R4</f>
-        <v>1226.0649707164766</v>
+        <f>R82*'Revenue Build'!R41</f>
+        <v>1288.9550040569832</v>
       </c>
       <c r="S80" s="342">
-        <f>S82*S17/S4</f>
-        <v>1231.657242357557</v>
+        <f>S82*'Revenue Build'!S41</f>
+        <v>1270.6438302453926</v>
       </c>
       <c r="T80" s="342">
-        <f>S80</f>
-        <v>1231.657242357557</v>
+        <f>T82*'Revenue Build'!T41</f>
+        <v>1270.6438302453928</v>
       </c>
       <c r="U80" s="342">
-        <f>U82*U17/U4</f>
-        <v>1283.5149885902601</v>
+        <f>U82*'Revenue Build'!U41</f>
+        <v>1357.621211088171</v>
       </c>
       <c r="V80" s="342">
-        <f>V82*V17/V4</f>
-        <v>1398.0214143744395</v>
+        <f>V82*'Revenue Build'!V41</f>
+        <v>1436.229919580297</v>
       </c>
       <c r="W80" s="342">
-        <f>W82*W17/W4</f>
-        <v>1501.7220633673348</v>
+        <f>W82*'Revenue Build'!W41</f>
+        <v>1509.3350482650096</v>
       </c>
     </row>
     <row r="81" outlineLevel="1" s="20">
@@ -6683,143 +6678,139 @@
       </c>
       <c r="L81" s="343">
         <f>L80</f>
-        <v>1053.9795662454812</v>
+        <v>1168.016098136345</v>
       </c>
       <c r="M81" s="343">
         <f>M80</f>
-        <v>1120.2065449601482</v>
+        <v>1204.6856730964362</v>
       </c>
       <c r="N81" s="343">
         <f>N80</f>
-        <v>1135.1385433257492</v>
+        <v>1189.1452899920976</v>
       </c>
       <c r="O81" s="343">
         <f>O80</f>
-        <v>1135.1385433257492</v>
+        <v>1189.1452899920976</v>
       </c>
       <c r="P81" s="343">
         <f>P80</f>
-        <v>1097.8660609023982</v>
+        <v>1190.2675400545152</v>
       </c>
       <c r="Q81" s="343">
         <f>Q80</f>
-        <v>1158.3448803324538</v>
+        <v>1254.213252213829</v>
       </c>
       <c r="R81" s="343">
         <f>R80</f>
-        <v>1226.0649707164766</v>
+        <v>1288.9550040569832</v>
       </c>
       <c r="S81" s="343">
         <f>S80</f>
-        <v>1231.657242357557</v>
+        <v>1270.6438302453926</v>
       </c>
       <c r="T81" s="343">
         <f>T80</f>
-        <v>1231.657242357557</v>
+        <v>1270.6438302453928</v>
       </c>
       <c r="U81" s="343">
         <f>U80</f>
-        <v>1283.5149885902601</v>
+        <v>1357.621211088171</v>
       </c>
       <c r="V81" s="343">
         <f>V80</f>
-        <v>1398.0214143744395</v>
+        <v>1436.229919580297</v>
       </c>
       <c r="W81" s="343">
         <f>W80</f>
-        <v>1501.7220633673348</v>
+        <v>1509.3350482650096</v>
       </c>
     </row>
     <row r="82" outlineLevel="1" s="20">
       <c r="B82" s="167" t="inlineStr">
         <is>
-          <t>Accounts payable - days of revenue (DPO)</t>
+          <t>Accounts payable - % of Net Earning Assets</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>days</t>
-        </is>
-      </c>
-      <c r="D82" s="344">
-        <f>D80/D17*D4</f>
-        <v>460.0126661185806</v>
+          <t>%</t>
+        </is>
       </c>
       <c r="E82" s="344">
-        <f>E80/E17*E4</f>
-        <v>450.3446320203024</v>
+        <f>E80/'Revenue Build'!E41</f>
+        <v>0.18074525738668815</v>
       </c>
       <c r="F82" s="344">
-        <f>F80/F17*F4</f>
-        <v>401.02107222014644</v>
+        <f>F80/'Revenue Build'!F41</f>
+        <v>0.16211963491762446</v>
       </c>
       <c r="G82" s="344">
-        <f>G80/G17*G4</f>
-        <v>427.4925385999876</v>
+        <f>G80/'Revenue Build'!G41</f>
+        <v>0.16434666861274774</v>
       </c>
       <c r="H82" s="344">
-        <f>H80/H17*H4</f>
-        <v>443.4848004177682</v>
+        <f>H80/'Revenue Build'!H41</f>
+        <v>0.1680175654381053</v>
       </c>
       <c r="I82" s="344">
-        <f>I80/I17*I4</f>
-        <v>366.6735242786905</v>
+        <f>I80/'Revenue Build'!I41</f>
+        <v>0.1410663341169392</v>
       </c>
       <c r="J82" s="344">
-        <f>J80/J17*J4</f>
-        <v>384.60084267530425</v>
+        <f>J80/'Revenue Build'!J41</f>
+        <v>0.1410663341169392</v>
       </c>
       <c r="K82" s="344">
-        <f>K80/K17*K4</f>
-        <v>306.72458240087036</v>
+        <f>K80/'Revenue Build'!K41</f>
+        <v>0.13064267662270554</v>
       </c>
       <c r="L82" s="345">
         <f>$K$82</f>
-        <v>306.72458240087036</v>
+        <v>0.13064267662270554</v>
       </c>
       <c r="M82" s="345">
         <f>$K$82</f>
-        <v>306.72458240087036</v>
+        <v>0.13064267662270554</v>
       </c>
       <c r="N82" s="345">
         <f>$K$82</f>
-        <v>306.72458240087036</v>
+        <v>0.13064267662270554</v>
       </c>
       <c r="O82" s="345">
-        <f>O80/O17*O4</f>
-        <v>315.6310053765508</v>
+        <f>$K$82</f>
+        <v>0.13064267662270554</v>
       </c>
       <c r="P82" s="345">
         <f>$K$82</f>
-        <v>306.72458240087036</v>
+        <v>0.13064267662270554</v>
       </c>
       <c r="Q82" s="345">
         <f>$K$82</f>
-        <v>306.72458240087036</v>
+        <v>0.13064267662270554</v>
       </c>
       <c r="R82" s="345">
         <f>$K$82</f>
-        <v>306.72458240087036</v>
+        <v>0.13064267662270554</v>
       </c>
       <c r="S82" s="345">
         <f>$K$82</f>
-        <v>306.72458240087036</v>
+        <v>0.13064267662270554</v>
       </c>
       <c r="T82" s="345">
-        <f>T80/T17*T4</f>
-        <v>318.8116907488106</v>
+        <f>$K$82</f>
+        <v>0.13064267662270554</v>
       </c>
       <c r="U82" s="345">
         <f>$K$82</f>
-        <v>306.72458240087036</v>
+        <v>0.13064267662270554</v>
       </c>
       <c r="V82" s="345">
         <f>$K$82</f>
-        <v>306.72458240087036</v>
+        <v>0.13064267662270554</v>
       </c>
       <c r="W82" s="345">
         <f>$K$82</f>
-        <v>306.72458240087036</v>
+        <v>0.13064267662270554</v>
       </c>
     </row>
     <row r="83" outlineLevel="1" s="20">
@@ -6862,51 +6853,51 @@
       </c>
       <c r="L83" s="346">
         <f>L76-L80</f>
-        <v>-814.7509568461087</v>
+        <v>-902.9038740838353</v>
       </c>
       <c r="M83" s="346">
         <f>M76-M80</f>
-        <v>-865.9459666972145</v>
+        <v>-931.2503166930613</v>
       </c>
       <c r="N83" s="346">
         <f>N76-N80</f>
-        <v>-877.4887521037055</v>
+        <v>-919.2372355959408</v>
       </c>
       <c r="O83" s="346">
         <f>O76-O80</f>
-        <v>-877.4887521037055</v>
+        <v>-919.2372355959408</v>
       </c>
       <c r="P83" s="346">
         <f>P76-P80</f>
-        <v>-848.676247866425</v>
+        <v>-920.1047612496234</v>
       </c>
       <c r="Q83" s="346">
         <f>Q76-Q80</f>
-        <v>-895.4277955981238</v>
+        <v>-969.5362984791338</v>
       </c>
       <c r="R83" s="346">
         <f>R76-R80</f>
-        <v>-947.7770158345594</v>
+        <v>-996.3924885450874</v>
       </c>
       <c r="S83" s="346">
         <f>S76-S80</f>
-        <v>-952.0999731445802</v>
+        <v>-982.2375211607443</v>
       </c>
       <c r="T83" s="346">
         <f>T76-T80</f>
-        <v>-952.0999731445802</v>
+        <v>-982.2375211607446</v>
       </c>
       <c r="U83" s="346">
         <f>U76-U80</f>
-        <v>-992.1872288334984</v>
+        <v>-1049.4730791688178</v>
       </c>
       <c r="V83" s="346">
         <f>V76-V80</f>
-        <v>-1080.7033850859611</v>
+        <v>-1110.2394569161065</v>
       </c>
       <c r="W83" s="346">
         <f>W76-W80</f>
-        <v>-1160.8664221109555</v>
+        <v>-1166.7514382236786</v>
       </c>
     </row>
     <row r="84" outlineLevel="1" s="20">
@@ -6937,7 +6928,7 @@
       <c r="N84" s="336" t="n"/>
       <c r="O84" s="335">
         <f>-O83/O13</f>
-        <v>1.2883969943477445</v>
+        <v>1.3496953534674696</v>
       </c>
       <c r="P84" s="336" t="n"/>
       <c r="Q84" s="336" t="n"/>
@@ -6945,19 +6936,19 @@
       <c r="S84" s="336" t="n"/>
       <c r="T84" s="335">
         <f>-T83/T13</f>
-        <v>1.2594868621301056</v>
+        <v>1.2993543622391621</v>
       </c>
       <c r="U84" s="335">
         <f>-U83/U13</f>
-        <v>1.1793552275755412</v>
+        <v>1.2474475846385311</v>
       </c>
       <c r="V84" s="335">
         <f>-V83/V13</f>
-        <v>1.1657852538106328</v>
+        <v>1.1976466484081303</v>
       </c>
       <c r="W84" s="335">
         <f>-W83/W13</f>
-        <v>1.1478961513177866</v>
+        <v>1.153715414600425</v>
       </c>
     </row>
     <row r="85" outlineLevel="1" ht="5.1" customHeight="1" s="20">
@@ -7026,51 +7017,51 @@
       </c>
       <c r="L87" s="197">
         <f>L83-K83</f>
-        <v>37.55304315389128</v>
+        <v>-50.59987408383529</v>
       </c>
       <c r="M87" s="197">
         <f>M83-L83</f>
-        <v>-51.19500985110585</v>
+        <v>-28.346442609226074</v>
       </c>
       <c r="N87" s="197">
         <f>N83-M83</f>
-        <v>-11.542785406490907</v>
+        <v>12.013081097120562</v>
       </c>
       <c r="O87" s="197">
         <f>O83-J83</f>
-        <v>126.59424789629452</v>
+        <v>84.8457644040592</v>
       </c>
       <c r="P87" s="197">
         <f>P83-O83</f>
-        <v>28.81250423728045</v>
+        <v>-0.8675256536826055</v>
       </c>
       <c r="Q87" s="197">
         <f>Q83-P83</f>
-        <v>-46.75154773169879</v>
+        <v>-49.43153722951047</v>
       </c>
       <c r="R87" s="197">
         <f>R83-Q83</f>
-        <v>-52.3492202364356</v>
+        <v>-26.85619006595357</v>
       </c>
       <c r="S87" s="197">
         <f>S83-R83</f>
-        <v>-4.322957310020797</v>
+        <v>14.154967384343081</v>
       </c>
       <c r="T87" s="197">
         <f>T83-O83</f>
-        <v>-74.61122104087474</v>
+        <v>-63.00028556480379</v>
       </c>
       <c r="U87" s="197">
         <f>U83-T83</f>
-        <v>-40.08725568891816</v>
+        <v>-67.23555800807321</v>
       </c>
       <c r="V87" s="197">
         <f>V83-U83</f>
-        <v>-88.51615625246279</v>
+        <v>-60.76637774728874</v>
       </c>
       <c r="W87" s="197">
         <f>W83-V83</f>
-        <v>-80.16303702499431</v>
+        <v>-56.511981307572114</v>
       </c>
       <c r="X87" s="330" t="n"/>
       <c r="Y87" s="330" t="n"/>
@@ -7384,7 +7375,7 @@
       <c r="N94" s="351" t="n"/>
       <c r="O94" s="197">
         <f>O55+O26+O39+O32+O29-O87-O89</f>
-        <v>438.8686836714917</v>
+        <v>480.617167163727</v>
       </c>
       <c r="P94" s="351" t="n"/>
       <c r="Q94" s="351" t="n"/>
@@ -7392,19 +7383,19 @@
       <c r="S94" s="351" t="n"/>
       <c r="T94" s="197">
         <f>T55+T26+T39+T32+T29-T87-T89</f>
-        <v>698.95290710438</v>
+        <v>687.341971628309</v>
       </c>
       <c r="U94" s="197">
         <f>U55+U26+U39+U32+U29-U87-U89</f>
-        <v>734.1543766834593</v>
+        <v>761.3026790026144</v>
       </c>
       <c r="V94" s="197">
         <f>V55+V26+V39+V32+V29-V87-V89</f>
-        <v>860.2982198396369</v>
+        <v>832.5484413344628</v>
       </c>
       <c r="W94" s="197">
         <f>W55+W26+W39+W32+W29-W87-W89</f>
-        <v>924.5560914934139</v>
+        <v>900.9050357759917</v>
       </c>
     </row>
     <row r="95" outlineLevel="1" s="20">
@@ -7431,7 +7422,7 @@
       <c r="N95" s="351" t="n"/>
       <c r="O95" s="197">
         <f>O94/O100</f>
-        <v>1.1038067204111275</v>
+        <v>1.2088091012148499</v>
       </c>
       <c r="P95" s="351" t="n"/>
       <c r="Q95" s="351" t="n"/>
@@ -7439,19 +7430,19 @@
       <c r="S95" s="351" t="n"/>
       <c r="T95" s="197">
         <f>T94/T100</f>
-        <v>1.7583735114910197</v>
+        <v>1.729163587364178</v>
       </c>
       <c r="U95" s="197">
         <f>U94/U100</f>
-        <v>1.8465631927491908</v>
+        <v>1.9148472722293761</v>
       </c>
       <c r="V95" s="197">
         <f>V94/V100</f>
-        <v>2.1638432978088336</v>
+        <v>2.094046370592951</v>
       </c>
       <c r="W95" s="197">
         <f>W94/W100</f>
-        <v>2.3254662812149878</v>
+        <v>2.265978562630859</v>
       </c>
     </row>
     <row r="96" outlineLevel="1" s="20">
@@ -7478,7 +7469,7 @@
       <c r="N96" s="351" t="n"/>
       <c r="O96" s="353">
         <f>O94/O17</f>
-        <v>0.3343278195917935</v>
+        <v>0.3661315913725816</v>
       </c>
       <c r="P96" s="351" t="n"/>
       <c r="Q96" s="351" t="n"/>
@@ -7486,19 +7477,19 @@
       <c r="S96" s="351" t="n"/>
       <c r="T96" s="353">
         <f>T94/T17</f>
-        <v>0.4956777499460561</v>
+        <v>0.487443600959695</v>
       </c>
       <c r="U96" s="353">
         <f>U94/U17</f>
-        <v>0.47935134029623877</v>
+        <v>0.4970772784868456</v>
       </c>
       <c r="V96" s="353">
         <f>V94/V17</f>
-        <v>0.5171195059221754</v>
+        <v>0.5004392996644892</v>
       </c>
       <c r="W96" s="353">
         <f>W94/W17</f>
-        <v>0.5173678317807281</v>
+        <v>0.5041330529193581</v>
       </c>
     </row>
     <row r="97" ht="14.45" customHeight="1" s="20">

--- a/EFN_Modelv2.xlsx
+++ b/EFN_Modelv2.xlsx
@@ -6314,51 +6314,51 @@
       </c>
       <c r="L76" s="342">
         <f>L78*'Revenue Build'!L41</f>
-        <v>265.1122240525096</v>
+        <v>247.45152942387315</v>
       </c>
       <c r="M76" s="342">
         <f>M78*'Revenue Build'!M41</f>
-        <v>273.43535640337484</v>
+        <v>255.2202086584112</v>
       </c>
       <c r="N76" s="342">
         <f>N78*'Revenue Build'!N41</f>
-        <v>269.90805439615684</v>
+        <v>251.92788111845923</v>
       </c>
       <c r="O76" s="342">
         <f>O78*'Revenue Build'!O41</f>
-        <v>269.90805439615684</v>
+        <v>251.92788111845923</v>
       </c>
       <c r="P76" s="342">
         <f>P78*'Revenue Build'!P41</f>
-        <v>270.1627788048918</v>
+        <v>252.16563682643655</v>
       </c>
       <c r="Q76" s="342">
         <f>Q78*'Revenue Build'!Q41</f>
-        <v>284.6769537346952</v>
+        <v>265.7129366446227</v>
       </c>
       <c r="R76" s="342">
         <f>R78*'Revenue Build'!R41</f>
-        <v>292.5625155118958</v>
+        <v>273.07319447169385</v>
       </c>
       <c r="S76" s="342">
         <f>S78*'Revenue Build'!S41</f>
-        <v>288.4063090846482</v>
+        <v>269.1938575580552</v>
       </c>
       <c r="T76" s="342">
         <f>T78*'Revenue Build'!T41</f>
-        <v>288.4063090846483</v>
+        <v>269.19385755805524</v>
       </c>
       <c r="U76" s="342">
         <f>U78*'Revenue Build'!U41</f>
-        <v>308.1481319193533</v>
+        <v>287.6205607080968</v>
       </c>
       <c r="V76" s="342">
         <f>V78*'Revenue Build'!V41</f>
-        <v>325.9904626641905</v>
+        <v>304.27430818079756</v>
       </c>
       <c r="W76" s="342">
         <f>W78*'Revenue Build'!W41</f>
-        <v>342.5836100413311</v>
+        <v>319.7620877847132</v>
       </c>
     </row>
     <row r="77" outlineLevel="1" s="20">
@@ -6402,51 +6402,51 @@
       </c>
       <c r="L77" s="343">
         <f>L76</f>
-        <v>265.1122240525096</v>
+        <v>247.45152942387315</v>
       </c>
       <c r="M77" s="343">
         <f>M76</f>
-        <v>273.43535640337484</v>
+        <v>255.2202086584112</v>
       </c>
       <c r="N77" s="343">
         <f>N76</f>
-        <v>269.90805439615684</v>
+        <v>251.92788111845923</v>
       </c>
       <c r="O77" s="343">
         <f>O76</f>
-        <v>269.90805439615684</v>
+        <v>251.92788111845923</v>
       </c>
       <c r="P77" s="343">
         <f>P76</f>
-        <v>270.1627788048918</v>
+        <v>252.16563682643655</v>
       </c>
       <c r="Q77" s="343">
         <f>Q76</f>
-        <v>284.6769537346952</v>
+        <v>265.7129366446227</v>
       </c>
       <c r="R77" s="343">
         <f>R76</f>
-        <v>292.5625155118958</v>
+        <v>273.07319447169385</v>
       </c>
       <c r="S77" s="343">
         <f>S76</f>
-        <v>288.4063090846482</v>
+        <v>269.1938575580552</v>
       </c>
       <c r="T77" s="343">
         <f>T76</f>
-        <v>288.4063090846483</v>
+        <v>269.19385755805524</v>
       </c>
       <c r="U77" s="343">
         <f>U76</f>
-        <v>308.1481319193533</v>
+        <v>287.6205607080968</v>
       </c>
       <c r="V77" s="343">
         <f>V76</f>
-        <v>325.9904626641905</v>
+        <v>304.27430818079756</v>
       </c>
       <c r="W77" s="343">
         <f>W76</f>
-        <v>342.5836100413311</v>
+        <v>319.7620877847132</v>
       </c>
     </row>
     <row r="78" outlineLevel="1" ht="5.1" customHeight="1" s="20">
@@ -6489,52 +6489,52 @@
         <v>0.029652819520964567</v>
       </c>
       <c r="L78" s="345">
-        <f>$K$78</f>
-        <v>0.029652819520964567</v>
+        <f>$J$78</f>
+        <v>0.02767746967691475</v>
       </c>
       <c r="M78" s="345">
-        <f>$K$78</f>
-        <v>0.029652819520964567</v>
+        <f>L78</f>
+        <v>0.02767746967691475</v>
       </c>
       <c r="N78" s="345">
-        <f>$K$78</f>
-        <v>0.029652819520964567</v>
+        <f>M78</f>
+        <v>0.02767746967691475</v>
       </c>
       <c r="O78" s="345">
-        <f>$K$78</f>
-        <v>0.029652819520964567</v>
+        <f>N78</f>
+        <v>0.02767746967691475</v>
       </c>
       <c r="P78" s="345">
-        <f>$K$78</f>
-        <v>0.029652819520964567</v>
+        <f>O78</f>
+        <v>0.02767746967691475</v>
       </c>
       <c r="Q78" s="345">
-        <f>$K$78</f>
-        <v>0.029652819520964567</v>
+        <f>P78</f>
+        <v>0.02767746967691475</v>
       </c>
       <c r="R78" s="345">
-        <f>$K$78</f>
-        <v>0.029652819520964567</v>
+        <f>Q78</f>
+        <v>0.02767746967691475</v>
       </c>
       <c r="S78" s="345">
-        <f>$K$78</f>
-        <v>0.029652819520964567</v>
+        <f>R78</f>
+        <v>0.02767746967691475</v>
       </c>
       <c r="T78" s="345">
-        <f>$K$78</f>
-        <v>0.029652819520964567</v>
+        <f>S78</f>
+        <v>0.02767746967691475</v>
       </c>
       <c r="U78" s="345">
-        <f>$K$78</f>
-        <v>0.029652819520964567</v>
+        <f>T78</f>
+        <v>0.02767746967691475</v>
       </c>
       <c r="V78" s="345">
-        <f>$K$78</f>
-        <v>0.029652819520964567</v>
+        <f>U78</f>
+        <v>0.02767746967691475</v>
       </c>
       <c r="W78" s="345">
-        <f>$K$78</f>
-        <v>0.029652819520964567</v>
+        <f>V78</f>
+        <v>0.02767746967691475</v>
       </c>
     </row>
     <row r="79" outlineLevel="1" s="20">
@@ -6590,51 +6590,51 @@
       </c>
       <c r="L80" s="342">
         <f>L82*'Revenue Build'!L41</f>
-        <v>1168.016098136345</v>
+        <v>1261.209226671867</v>
       </c>
       <c r="M80" s="342">
         <f>M82*'Revenue Build'!M41</f>
-        <v>1204.6856730964362</v>
+        <v>1300.8045767287667</v>
       </c>
       <c r="N80" s="342">
         <f>N82*'Revenue Build'!N41</f>
-        <v>1189.1452899920976</v>
+        <v>1284.0242647206703</v>
       </c>
       <c r="O80" s="342">
         <f>O82*'Revenue Build'!O41</f>
-        <v>1189.1452899920976</v>
+        <v>1284.0242647206703</v>
       </c>
       <c r="P80" s="342">
         <f>P82*'Revenue Build'!P41</f>
-        <v>1190.2675400545152</v>
+        <v>1285.2360563523205</v>
       </c>
       <c r="Q80" s="342">
         <f>Q82*'Revenue Build'!Q41</f>
-        <v>1254.213252213829</v>
+        <v>1354.2838394352004</v>
       </c>
       <c r="R80" s="342">
         <f>R82*'Revenue Build'!R41</f>
-        <v>1288.9550040569832</v>
+        <v>1391.7975501154237</v>
       </c>
       <c r="S80" s="342">
         <f>S82*'Revenue Build'!S41</f>
-        <v>1270.6438302453926</v>
+        <v>1372.0253728318924</v>
       </c>
       <c r="T80" s="342">
         <f>T82*'Revenue Build'!T41</f>
-        <v>1270.6438302453928</v>
+        <v>1372.0253728318926</v>
       </c>
       <c r="U80" s="342">
         <f>U82*'Revenue Build'!U41</f>
-        <v>1357.621211088171</v>
+        <v>1465.942464733018</v>
       </c>
       <c r="V80" s="342">
         <f>V82*'Revenue Build'!V41</f>
-        <v>1436.229919580297</v>
+        <v>1550.8231685223036</v>
       </c>
       <c r="W80" s="342">
         <f>W82*'Revenue Build'!W41</f>
-        <v>1509.3350482650096</v>
+        <v>1629.7611754224713</v>
       </c>
     </row>
     <row r="81" outlineLevel="1" s="20">
@@ -6678,51 +6678,51 @@
       </c>
       <c r="L81" s="343">
         <f>L80</f>
-        <v>1168.016098136345</v>
+        <v>1261.209226671867</v>
       </c>
       <c r="M81" s="343">
         <f>M80</f>
-        <v>1204.6856730964362</v>
+        <v>1300.8045767287667</v>
       </c>
       <c r="N81" s="343">
         <f>N80</f>
-        <v>1189.1452899920976</v>
+        <v>1284.0242647206703</v>
       </c>
       <c r="O81" s="343">
         <f>O80</f>
-        <v>1189.1452899920976</v>
+        <v>1284.0242647206703</v>
       </c>
       <c r="P81" s="343">
         <f>P80</f>
-        <v>1190.2675400545152</v>
+        <v>1285.2360563523205</v>
       </c>
       <c r="Q81" s="343">
         <f>Q80</f>
-        <v>1254.213252213829</v>
+        <v>1354.2838394352004</v>
       </c>
       <c r="R81" s="343">
         <f>R80</f>
-        <v>1288.9550040569832</v>
+        <v>1391.7975501154237</v>
       </c>
       <c r="S81" s="343">
         <f>S80</f>
-        <v>1270.6438302453926</v>
+        <v>1372.0253728318924</v>
       </c>
       <c r="T81" s="343">
         <f>T80</f>
-        <v>1270.6438302453928</v>
+        <v>1372.0253728318926</v>
       </c>
       <c r="U81" s="343">
         <f>U80</f>
-        <v>1357.621211088171</v>
+        <v>1465.942464733018</v>
       </c>
       <c r="V81" s="343">
         <f>V80</f>
-        <v>1436.229919580297</v>
+        <v>1550.8231685223036</v>
       </c>
       <c r="W81" s="343">
         <f>W80</f>
-        <v>1509.3350482650096</v>
+        <v>1629.7611754224713</v>
       </c>
     </row>
     <row r="82" outlineLevel="1" s="20">
@@ -6765,52 +6765,52 @@
         <v>0.13064267662270554</v>
       </c>
       <c r="L82" s="345">
-        <f>$K$82</f>
-        <v>0.13064267662270554</v>
+        <f>$J$82</f>
+        <v>0.1410663341169392</v>
       </c>
       <c r="M82" s="345">
-        <f>$K$82</f>
-        <v>0.13064267662270554</v>
+        <f>L82</f>
+        <v>0.1410663341169392</v>
       </c>
       <c r="N82" s="345">
-        <f>$K$82</f>
-        <v>0.13064267662270554</v>
+        <f>M82</f>
+        <v>0.1410663341169392</v>
       </c>
       <c r="O82" s="345">
-        <f>$K$82</f>
-        <v>0.13064267662270554</v>
+        <f>N82</f>
+        <v>0.1410663341169392</v>
       </c>
       <c r="P82" s="345">
-        <f>$K$82</f>
-        <v>0.13064267662270554</v>
+        <f>O82</f>
+        <v>0.1410663341169392</v>
       </c>
       <c r="Q82" s="345">
-        <f>$K$82</f>
-        <v>0.13064267662270554</v>
+        <f>P82</f>
+        <v>0.1410663341169392</v>
       </c>
       <c r="R82" s="345">
-        <f>$K$82</f>
-        <v>0.13064267662270554</v>
+        <f>Q82</f>
+        <v>0.1410663341169392</v>
       </c>
       <c r="S82" s="345">
-        <f>$K$82</f>
-        <v>0.13064267662270554</v>
+        <f>R82</f>
+        <v>0.1410663341169392</v>
       </c>
       <c r="T82" s="345">
-        <f>$K$82</f>
-        <v>0.13064267662270554</v>
+        <f>S82</f>
+        <v>0.1410663341169392</v>
       </c>
       <c r="U82" s="345">
-        <f>$K$82</f>
-        <v>0.13064267662270554</v>
+        <f>T82</f>
+        <v>0.1410663341169392</v>
       </c>
       <c r="V82" s="345">
-        <f>$K$82</f>
-        <v>0.13064267662270554</v>
+        <f>U82</f>
+        <v>0.1410663341169392</v>
       </c>
       <c r="W82" s="345">
-        <f>$K$82</f>
-        <v>0.13064267662270554</v>
+        <f>V82</f>
+        <v>0.1410663341169392</v>
       </c>
     </row>
     <row r="83" outlineLevel="1" s="20">
@@ -6853,51 +6853,51 @@
       </c>
       <c r="L83" s="346">
         <f>L76-L80</f>
-        <v>-902.9038740838353</v>
+        <v>-1013.757697247994</v>
       </c>
       <c r="M83" s="346">
         <f>M76-M80</f>
-        <v>-931.2503166930613</v>
+        <v>-1045.5843680703556</v>
       </c>
       <c r="N83" s="346">
         <f>N76-N80</f>
-        <v>-919.2372355959408</v>
+        <v>-1032.096383602211</v>
       </c>
       <c r="O83" s="346">
         <f>O76-O80</f>
-        <v>-919.2372355959408</v>
+        <v>-1032.096383602211</v>
       </c>
       <c r="P83" s="346">
         <f>P76-P80</f>
-        <v>-920.1047612496234</v>
+        <v>-1033.0704195258838</v>
       </c>
       <c r="Q83" s="346">
         <f>Q76-Q80</f>
-        <v>-969.5362984791338</v>
+        <v>-1088.5709027905777</v>
       </c>
       <c r="R83" s="346">
         <f>R76-R80</f>
-        <v>-996.3924885450874</v>
+        <v>-1118.72435564373</v>
       </c>
       <c r="S83" s="346">
         <f>S76-S80</f>
-        <v>-982.2375211607443</v>
+        <v>-1102.831515273837</v>
       </c>
       <c r="T83" s="346">
         <f>T76-T80</f>
-        <v>-982.2375211607446</v>
+        <v>-1102.8315152738373</v>
       </c>
       <c r="U83" s="346">
         <f>U76-U80</f>
-        <v>-1049.4730791688178</v>
+        <v>-1178.3219040249212</v>
       </c>
       <c r="V83" s="346">
         <f>V76-V80</f>
-        <v>-1110.2394569161065</v>
+        <v>-1246.548860341506</v>
       </c>
       <c r="W83" s="346">
         <f>W76-W80</f>
-        <v>-1166.7514382236786</v>
+        <v>-1309.999087637758</v>
       </c>
     </row>
     <row r="84" outlineLevel="1" s="20">
@@ -6928,7 +6928,7 @@
       <c r="N84" s="336" t="n"/>
       <c r="O84" s="335">
         <f>-O83/O13</f>
-        <v>1.3496953534674696</v>
+        <v>1.5154039015569167</v>
       </c>
       <c r="P84" s="336" t="n"/>
       <c r="Q84" s="336" t="n"/>
@@ -6936,19 +6936,19 @@
       <c r="S84" s="336" t="n"/>
       <c r="T84" s="335">
         <f>-T83/T13</f>
-        <v>1.2993543622391621</v>
+        <v>1.458882306280151</v>
       </c>
       <c r="U84" s="335">
         <f>-U83/U13</f>
-        <v>1.2474475846385311</v>
+        <v>1.4006026855559928</v>
       </c>
       <c r="V84" s="335">
         <f>-V83/V13</f>
-        <v>1.1976466484081303</v>
+        <v>1.3446874504098891</v>
       </c>
       <c r="W84" s="335">
         <f>-W83/W13</f>
-        <v>1.153715414600425</v>
+        <v>1.2953625691013972</v>
       </c>
     </row>
     <row r="85" outlineLevel="1" ht="5.1" customHeight="1" s="20">
@@ -7017,51 +7017,51 @@
       </c>
       <c r="L87" s="197">
         <f>L83-K83</f>
-        <v>-50.59987408383529</v>
+        <v>-161.453697247994</v>
       </c>
       <c r="M87" s="197">
         <f>M83-L83</f>
-        <v>-28.346442609226074</v>
+        <v>-31.82667082236162</v>
       </c>
       <c r="N87" s="197">
         <f>N83-M83</f>
-        <v>12.013081097120562</v>
+        <v>13.487984468144532</v>
       </c>
       <c r="O87" s="197">
         <f>O83-J83</f>
-        <v>84.8457644040592</v>
+        <v>-28.013383602211093</v>
       </c>
       <c r="P87" s="197">
         <f>P83-O83</f>
-        <v>-0.8675256536826055</v>
+        <v>-0.9740359236727727</v>
       </c>
       <c r="Q87" s="197">
         <f>Q83-P83</f>
-        <v>-49.43153722951047</v>
+        <v>-55.50048326469391</v>
       </c>
       <c r="R87" s="197">
         <f>R83-Q83</f>
-        <v>-26.85619006595357</v>
+        <v>-30.153452853152203</v>
       </c>
       <c r="S87" s="197">
         <f>S83-R83</f>
-        <v>14.154967384343081</v>
+        <v>15.892840369892838</v>
       </c>
       <c r="T87" s="197">
         <f>T83-O83</f>
-        <v>-63.00028556480379</v>
+        <v>-70.73513167162628</v>
       </c>
       <c r="U87" s="197">
         <f>U83-T83</f>
-        <v>-67.23555800807321</v>
+        <v>-75.49038875108386</v>
       </c>
       <c r="V87" s="197">
         <f>V83-U83</f>
-        <v>-60.76637774728874</v>
+        <v>-68.22695631658485</v>
       </c>
       <c r="W87" s="197">
         <f>W83-V83</f>
-        <v>-56.511981307572114</v>
+        <v>-63.450227296252024</v>
       </c>
       <c r="X87" s="330" t="n"/>
       <c r="Y87" s="330" t="n"/>
@@ -7375,7 +7375,7 @@
       <c r="N94" s="351" t="n"/>
       <c r="O94" s="197">
         <f>O55+O26+O39+O32+O29-O87-O89</f>
-        <v>480.617167163727</v>
+        <v>593.4763151699973</v>
       </c>
       <c r="P94" s="351" t="n"/>
       <c r="Q94" s="351" t="n"/>
@@ -7383,19 +7383,19 @@
       <c r="S94" s="351" t="n"/>
       <c r="T94" s="197">
         <f>T55+T26+T39+T32+T29-T87-T89</f>
-        <v>687.341971628309</v>
+        <v>695.0768177351315</v>
       </c>
       <c r="U94" s="197">
         <f>U55+U26+U39+U32+U29-U87-U89</f>
-        <v>761.3026790026144</v>
+        <v>769.557509745625</v>
       </c>
       <c r="V94" s="197">
         <f>V55+V26+V39+V32+V29-V87-V89</f>
-        <v>832.5484413344628</v>
+        <v>840.0090199037589</v>
       </c>
       <c r="W94" s="197">
         <f>W55+W26+W39+W32+W29-W87-W89</f>
-        <v>900.9050357759917</v>
+        <v>907.8432817646716</v>
       </c>
     </row>
     <row r="95" outlineLevel="1" s="20">
@@ -7422,7 +7422,7 @@
       <c r="N95" s="351" t="n"/>
       <c r="O95" s="197">
         <f>O94/O100</f>
-        <v>1.2088091012148499</v>
+        <v>1.4926632258405288</v>
       </c>
       <c r="P95" s="351" t="n"/>
       <c r="Q95" s="351" t="n"/>
@@ -7430,19 +7430,19 @@
       <c r="S95" s="351" t="n"/>
       <c r="T95" s="197">
         <f>T94/T100</f>
-        <v>1.729163587364178</v>
+        <v>1.7486223354020698</v>
       </c>
       <c r="U95" s="197">
         <f>U94/U100</f>
-        <v>1.9148472722293761</v>
+        <v>1.935610026081336</v>
       </c>
       <c r="V95" s="197">
         <f>V94/V100</f>
-        <v>2.094046370592951</v>
+        <v>2.1128114017910353</v>
       </c>
       <c r="W95" s="197">
         <f>W94/W100</f>
-        <v>2.265978562630859</v>
+        <v>2.283429810041265</v>
       </c>
     </row>
     <row r="96" outlineLevel="1" s="20">
@@ -7469,7 +7469,7 @@
       <c r="N96" s="351" t="n"/>
       <c r="O96" s="353">
         <f>O94/O17</f>
-        <v>0.3661315913725816</v>
+        <v>0.45210708763780955</v>
       </c>
       <c r="P96" s="351" t="n"/>
       <c r="Q96" s="351" t="n"/>
@@ -7477,19 +7477,19 @@
       <c r="S96" s="351" t="n"/>
       <c r="T96" s="353">
         <f>T94/T17</f>
-        <v>0.487443600959695</v>
+        <v>0.49292893634558277</v>
       </c>
       <c r="U96" s="353">
         <f>U94/U17</f>
-        <v>0.4970772784868456</v>
+        <v>0.5024671042595343</v>
       </c>
       <c r="V96" s="353">
         <f>V94/V17</f>
-        <v>0.5004392996644892</v>
+        <v>0.5049238035431176</v>
       </c>
       <c r="W96" s="353">
         <f>W94/W17</f>
-        <v>0.5041330529193581</v>
+        <v>0.5080155921363421</v>
       </c>
     </row>
     <row r="97" ht="14.45" customHeight="1" s="20">

--- a/EFN_Modelv2.xlsx
+++ b/EFN_Modelv2.xlsx
@@ -499,7 +499,7 @@
     <xf numFmtId="9" fontId="33" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="34" fillId="9" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="418">
+  <cellXfs count="420">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1078,6 +1078,8 @@
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1584,7 +1586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB113"/>
+  <dimension ref="A1:AB128"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col width="10.5703125" customWidth="1" style="305" min="1" max="1"/>
@@ -7352,16 +7354,8 @@
       </c>
     </row>
     <row r="94" outlineLevel="1" s="20">
-      <c r="B94" s="89" t="inlineStr">
-        <is>
-          <t>Free Cash Flow</t>
-        </is>
-      </c>
-      <c r="C94" s="307" t="inlineStr">
-        <is>
-          <t>$</t>
-        </is>
-      </c>
+      <c r="B94" s="89" t="n"/>
+      <c r="C94" s="307" t="n"/>
       <c r="D94" s="351" t="n"/>
       <c r="E94" s="351" t="n"/>
       <c r="F94" s="351" t="n"/>
@@ -7373,42 +7367,19 @@
       <c r="L94" s="351" t="n"/>
       <c r="M94" s="351" t="n"/>
       <c r="N94" s="351" t="n"/>
-      <c r="O94" s="197">
-        <f>O55+O26+O39+O32+O29-O87-O89</f>
-        <v>593.4763151699973</v>
-      </c>
+      <c r="O94" s="197" t="n"/>
       <c r="P94" s="351" t="n"/>
       <c r="Q94" s="351" t="n"/>
       <c r="R94" s="351" t="n"/>
       <c r="S94" s="351" t="n"/>
-      <c r="T94" s="197">
-        <f>T55+T26+T39+T32+T29-T87-T89</f>
-        <v>695.0768177351315</v>
-      </c>
-      <c r="U94" s="197">
-        <f>U55+U26+U39+U32+U29-U87-U89</f>
-        <v>769.557509745625</v>
-      </c>
-      <c r="V94" s="197">
-        <f>V55+V26+V39+V32+V29-V87-V89</f>
-        <v>840.0090199037589</v>
-      </c>
-      <c r="W94" s="197">
-        <f>W55+W26+W39+W32+W29-W87-W89</f>
-        <v>907.8432817646716</v>
-      </c>
+      <c r="T94" s="197" t="n"/>
+      <c r="U94" s="197" t="n"/>
+      <c r="V94" s="197" t="n"/>
+      <c r="W94" s="197" t="n"/>
     </row>
     <row r="95" outlineLevel="1" s="20">
-      <c r="B95" s="89" t="inlineStr">
-        <is>
-          <t>FCF per Share</t>
-        </is>
-      </c>
-      <c r="C95" s="307" t="inlineStr">
-        <is>
-          <t>$</t>
-        </is>
-      </c>
+      <c r="B95" s="89" t="n"/>
+      <c r="C95" s="307" t="n"/>
       <c r="D95" s="351" t="n"/>
       <c r="E95" s="351" t="n"/>
       <c r="F95" s="351" t="n"/>
@@ -7420,42 +7391,19 @@
       <c r="L95" s="351" t="n"/>
       <c r="M95" s="351" t="n"/>
       <c r="N95" s="351" t="n"/>
-      <c r="O95" s="197">
-        <f>O94/O100</f>
-        <v>1.4926632258405288</v>
-      </c>
+      <c r="O95" s="197" t="n"/>
       <c r="P95" s="351" t="n"/>
       <c r="Q95" s="351" t="n"/>
       <c r="R95" s="351" t="n"/>
       <c r="S95" s="351" t="n"/>
-      <c r="T95" s="197">
-        <f>T94/T100</f>
-        <v>1.7486223354020698</v>
-      </c>
-      <c r="U95" s="197">
-        <f>U94/U100</f>
-        <v>1.935610026081336</v>
-      </c>
-      <c r="V95" s="197">
-        <f>V94/V100</f>
-        <v>2.1128114017910353</v>
-      </c>
-      <c r="W95" s="197">
-        <f>W94/W100</f>
-        <v>2.283429810041265</v>
-      </c>
+      <c r="T95" s="197" t="n"/>
+      <c r="U95" s="197" t="n"/>
+      <c r="V95" s="197" t="n"/>
+      <c r="W95" s="197" t="n"/>
     </row>
     <row r="96" outlineLevel="1" s="20">
-      <c r="B96" s="89" t="inlineStr">
-        <is>
-          <t>FCF Margin</t>
-        </is>
-      </c>
-      <c r="C96" s="307" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
+      <c r="B96" s="89" t="n"/>
+      <c r="C96" s="307" t="n"/>
       <c r="D96" s="351" t="n"/>
       <c r="E96" s="351" t="n"/>
       <c r="F96" s="351" t="n"/>
@@ -7467,30 +7415,15 @@
       <c r="L96" s="351" t="n"/>
       <c r="M96" s="351" t="n"/>
       <c r="N96" s="351" t="n"/>
-      <c r="O96" s="353">
-        <f>O94/O17</f>
-        <v>0.45210708763780955</v>
-      </c>
+      <c r="O96" s="353" t="n"/>
       <c r="P96" s="351" t="n"/>
       <c r="Q96" s="351" t="n"/>
       <c r="R96" s="351" t="n"/>
       <c r="S96" s="351" t="n"/>
-      <c r="T96" s="353">
-        <f>T94/T17</f>
-        <v>0.49292893634558277</v>
-      </c>
-      <c r="U96" s="353">
-        <f>U94/U17</f>
-        <v>0.5024671042595343</v>
-      </c>
-      <c r="V96" s="353">
-        <f>V94/V17</f>
-        <v>0.5049238035431176</v>
-      </c>
-      <c r="W96" s="353">
-        <f>W94/W17</f>
-        <v>0.5080155921363421</v>
-      </c>
+      <c r="T96" s="353" t="n"/>
+      <c r="U96" s="353" t="n"/>
+      <c r="V96" s="353" t="n"/>
+      <c r="W96" s="353" t="n"/>
     </row>
     <row r="97" ht="14.45" customHeight="1" s="20">
       <c r="B97" s="320" t="n"/>
@@ -8041,17 +7974,410 @@
       <c r="AB111" s="330" t="n"/>
     </row>
     <row r="112">
-      <c r="B112" s="325" t="inlineStr">
-        <is>
-          <t>Need to build out FCF/Share</t>
-        </is>
-      </c>
+      <c r="B112" s="325" t="n"/>
     </row>
     <row r="113">
       <c r="B113" s="307" t="inlineStr">
         <is>
           <t>Share buybacks</t>
         </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" s="82" t="inlineStr">
+        <is>
+          <t>Free Cash Flow Build</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" s="307" t="inlineStr">
+        <is>
+          <t>Net Income</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="O115" s="418">
+        <f>O55</f>
+        <v>493.6006060978542</v>
+      </c>
+      <c r="T115" s="418">
+        <f>T55</f>
+        <v>539.0756351169435</v>
+      </c>
+      <c r="U115" s="418">
+        <f>U55</f>
+        <v>594.5654048790257</v>
+      </c>
+      <c r="V115" s="418">
+        <f>V55</f>
+        <v>656.8006281804242</v>
+      </c>
+      <c r="W115" s="418">
+        <f>W55</f>
+        <v>714.9485348876021</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" s="307" t="inlineStr">
+        <is>
+          <t>(+) Depreciation &amp; amortization</t>
+        </is>
+      </c>
+      <c r="O116" s="418">
+        <f>O26</f>
+        <v>71.43155324828221</v>
+      </c>
+      <c r="T116" s="418">
+        <f>T26</f>
+        <v>77.16377781143325</v>
+      </c>
+      <c r="U116" s="418">
+        <f>U26</f>
+        <v>83.81050106647312</v>
+      </c>
+      <c r="V116" s="418">
+        <f>V26</f>
+        <v>91.03808116009077</v>
+      </c>
+      <c r="W116" s="418">
+        <f>W26</f>
+        <v>97.79098780536819</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" s="307" t="inlineStr">
+        <is>
+          <t>(+) Amortization of intangibles</t>
+        </is>
+      </c>
+      <c r="O117" s="418">
+        <f>O39</f>
+        <v>36.432945434556316</v>
+      </c>
+      <c r="T117" s="418">
+        <f>T39</f>
+        <v>38.938839105828066</v>
+      </c>
+      <c r="U117" s="418">
+        <f>U39</f>
+        <v>42.29294766232509</v>
+      </c>
+      <c r="V117" s="418">
+        <f>V39</f>
+        <v>45.94017161081564</v>
+      </c>
+      <c r="W117" s="418">
+        <f>W39</f>
+        <v>49.347863053809945</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" s="307" t="inlineStr">
+        <is>
+          <t>(+) Share-based compensation</t>
+        </is>
+      </c>
+      <c r="O118" s="418">
+        <f>O32</f>
+        <v>43.997826787093494</v>
+      </c>
+      <c r="T118" s="418">
+        <f>T32</f>
+        <v>49.16343402930033</v>
+      </c>
+      <c r="U118" s="418">
+        <f>U32</f>
+        <v>53.39826738671731</v>
+      </c>
+      <c r="V118" s="418">
+        <f>V32</f>
+        <v>58.00318263584351</v>
+      </c>
+      <c r="W118" s="418">
+        <f>W32</f>
+        <v>62.30566872163918</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" s="307" t="inlineStr">
+        <is>
+          <t>(+) Amortization of debenture discount</t>
+        </is>
+      </c>
+      <c r="O119" s="418">
+        <f>O29</f>
+        <v>0.0</v>
+      </c>
+      <c r="T119" s="418">
+        <f>T29</f>
+        <v>0.0</v>
+      </c>
+      <c r="U119" s="418">
+        <f>U29</f>
+        <v>0.0</v>
+      </c>
+      <c r="V119" s="418">
+        <f>V29</f>
+        <v>0.0</v>
+      </c>
+      <c r="W119" s="418">
+        <f>W29</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" s="307" t="inlineStr">
+        <is>
+          <t>(+/-) Decrease / (increase) in net working capital</t>
+        </is>
+      </c>
+      <c r="O120" s="418">
+        <f>-O87</f>
+        <v>28.013383602211093</v>
+      </c>
+      <c r="T120" s="418">
+        <f>-T87</f>
+        <v>70.73513167162628</v>
+      </c>
+      <c r="U120" s="418">
+        <f>-U87</f>
+        <v>75.49038875108386</v>
+      </c>
+      <c r="V120" s="418">
+        <f>-V87</f>
+        <v>68.22695631658485</v>
+      </c>
+      <c r="W120" s="418">
+        <f>-W87</f>
+        <v>63.450227296252024</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" s="307" t="inlineStr">
+        <is>
+          <t>(-) Capital expenditures</t>
+        </is>
+      </c>
+      <c r="O121" s="418">
+        <f>-O89</f>
+        <v>-80.0</v>
+      </c>
+      <c r="T121" s="418">
+        <f>-T89</f>
+        <v>-80.0</v>
+      </c>
+      <c r="U121" s="418">
+        <f>-U89</f>
+        <v>-80.0</v>
+      </c>
+      <c r="V121" s="418">
+        <f>-V89</f>
+        <v>-80.0</v>
+      </c>
+      <c r="W121" s="418">
+        <f>-W89</f>
+        <v>-80.0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" s="307" t="inlineStr">
+        <is>
+          <t>Free Cash Flow</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="O122" s="418">
+        <f>SUM(O115:O121)</f>
+        <v>593.4763151699973</v>
+      </c>
+      <c r="T122" s="418">
+        <f>SUM(T115:T121)</f>
+        <v>695.0768177351315</v>
+      </c>
+      <c r="U122" s="418">
+        <f>SUM(U115:U121)</f>
+        <v>769.557509745625</v>
+      </c>
+      <c r="V122" s="418">
+        <f>SUM(V115:V121)</f>
+        <v>840.0090199037589</v>
+      </c>
+      <c r="W122" s="418">
+        <f>SUM(W115:W121)</f>
+        <v>907.8432817646716</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" s="307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   % growth</t>
+        </is>
+      </c>
+      <c r="T123" s="344">
+        <f>T122/O122-1</f>
+        <v>0.17119554726633268</v>
+      </c>
+      <c r="U123" s="344">
+        <f>U122/T122-1</f>
+        <v>0.10715461961914463</v>
+      </c>
+      <c r="V123" s="344">
+        <f>V122/U122-1</f>
+        <v>0.09154807700001721</v>
+      </c>
+      <c r="W123" s="344">
+        <f>W122/V122-1</f>
+        <v>0.0807542065068354</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" s="307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   FCF margin (% net revenue)</t>
+        </is>
+      </c>
+      <c r="O124" s="344">
+        <f>O122/O17</f>
+        <v>0.45210708763780955</v>
+      </c>
+      <c r="T124" s="344">
+        <f>T122/T17</f>
+        <v>0.49292893634558277</v>
+      </c>
+      <c r="U124" s="344">
+        <f>U122/U17</f>
+        <v>0.5024671042595343</v>
+      </c>
+      <c r="V124" s="344">
+        <f>V122/V17</f>
+        <v>0.5049238035431176</v>
+      </c>
+      <c r="W124" s="344">
+        <f>W122/W17</f>
+        <v>0.5080155921363421</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" s="307" t="inlineStr">
+        <is>
+          <t>Diluted weighted-average shares</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="O125" s="418">
+        <f>O100</f>
+        <v>397.5955894778655</v>
+      </c>
+      <c r="T125" s="418">
+        <f>T100</f>
+        <v>397.4996794120835</v>
+      </c>
+      <c r="U125" s="418">
+        <f>U100</f>
+        <v>397.5787991259803</v>
+      </c>
+      <c r="V125" s="418">
+        <f>V100</f>
+        <v>397.5787991259803</v>
+      </c>
+      <c r="W125" s="418">
+        <f>W100</f>
+        <v>397.5787991259803</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" s="307" t="inlineStr">
+        <is>
+          <t>Free Cash Flow per Share</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="O126" s="419">
+        <f>O122/O125</f>
+        <v>1.4926632258405288</v>
+      </c>
+      <c r="T126" s="419">
+        <f>T122/T125</f>
+        <v>1.7486223354020698</v>
+      </c>
+      <c r="U126" s="419">
+        <f>U122/U125</f>
+        <v>1.935610026081336</v>
+      </c>
+      <c r="V126" s="419">
+        <f>V122/V125</f>
+        <v>2.1128114017910353</v>
+      </c>
+      <c r="W126" s="419">
+        <f>W122/W125</f>
+        <v>2.283429810041265</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" s="307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   % growth</t>
+        </is>
+      </c>
+      <c r="T127" s="344">
+        <f>T126/O126-1</f>
+        <v>0.17147813728539374</v>
+      </c>
+      <c r="U127" s="344">
+        <f>U126/T126-1</f>
+        <v>0.10693429158118994</v>
+      </c>
+      <c r="V127" s="344">
+        <f>V126/U126-1</f>
+        <v>0.09154807700001721</v>
+      </c>
+      <c r="W127" s="344">
+        <f>W126/V126-1</f>
+        <v>0.0807542065068354</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" s="307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   FCF yield (on current price)</t>
+        </is>
+      </c>
+      <c r="O128" s="344">
+        <f>O126*O110/O109</f>
+        <v>0.07350564714360913</v>
+      </c>
+      <c r="T128" s="344">
+        <f>T126*T110/T109</f>
+        <v>0.08611025859575266</v>
+      </c>
+      <c r="U128" s="344">
+        <f>U126*U110/U109</f>
+        <v>0.09531839809656253</v>
+      </c>
+      <c r="V128" s="344">
+        <f>V126*V110/V109</f>
+        <v>0.10404461414502493</v>
+      </c>
+      <c r="W128" s="344">
+        <f>W126*W110/W109</f>
+        <v>0.11244665440161629</v>
       </c>
     </row>
   </sheetData>

--- a/EFN_Modelv2.xlsx
+++ b/EFN_Modelv2.xlsx
@@ -7085,16 +7085,30 @@
       <c r="I89" s="303" t="n"/>
       <c r="J89" s="303" t="n"/>
       <c r="K89" s="304" t="n"/>
-      <c r="L89" s="303" t="n"/>
-      <c r="M89" s="303" t="n"/>
-      <c r="N89" s="303" t="n"/>
+      <c r="L89" s="303" t="n">
+        <v>20</v>
+      </c>
+      <c r="M89" s="303" t="n">
+        <v>20</v>
+      </c>
+      <c r="N89" s="303" t="n">
+        <v>20</v>
+      </c>
       <c r="O89" s="238" t="n">
         <v>80</v>
       </c>
-      <c r="P89" s="238" t="n"/>
-      <c r="Q89" s="238" t="n"/>
-      <c r="R89" s="238" t="n"/>
-      <c r="S89" s="238" t="n"/>
+      <c r="P89" s="238" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q89" s="238" t="n">
+        <v>20</v>
+      </c>
+      <c r="R89" s="238" t="n">
+        <v>20</v>
+      </c>
+      <c r="S89" s="238" t="n">
+        <v>20</v>
+      </c>
       <c r="T89" s="238" t="n">
         <v>80</v>
       </c>
@@ -8001,10 +8015,38 @@
           <t>$</t>
         </is>
       </c>
+      <c r="L115" s="418">
+        <f>L55</f>
+        <v>118.56365419179409</v>
+      </c>
+      <c r="M115" s="418">
+        <f>M55</f>
+        <v>127.39838589081758</v>
+      </c>
+      <c r="N115" s="418">
+        <f>N55</f>
+        <v>129.0965660152424</v>
+      </c>
       <c r="O115" s="418">
         <f>O55</f>
         <v>493.6006060978542</v>
       </c>
+      <c r="P115" s="418">
+        <f>P55</f>
+        <v>122.14335969256284</v>
+      </c>
+      <c r="Q115" s="418">
+        <f>Q55</f>
+        <v>130.3038561893571</v>
+      </c>
+      <c r="R115" s="418">
+        <f>R55</f>
+        <v>139.4374090825442</v>
+      </c>
+      <c r="S115" s="418">
+        <f>S55</f>
+        <v>140.0734046350983</v>
+      </c>
       <c r="T115" s="418">
         <f>T55</f>
         <v>539.0756351169435</v>
@@ -8028,10 +8070,38 @@
           <t>(+) Depreciation &amp; amortization</t>
         </is>
       </c>
+      <c r="L116" s="418">
+        <f>L26</f>
+        <v>17.19838588667246</v>
+      </c>
+      <c r="M116" s="418">
+        <f>M26</f>
+        <v>18.47991795483252</v>
+      </c>
+      <c r="N116" s="418">
+        <f>N26</f>
+        <v>18.726249406777224</v>
+      </c>
       <c r="O116" s="418">
         <f>O26</f>
         <v>71.43155324828221</v>
       </c>
+      <c r="P116" s="418">
+        <f>P26</f>
+        <v>17.717644144884325</v>
+      </c>
+      <c r="Q116" s="418">
+        <f>Q26</f>
+        <v>18.901374257922797</v>
+      </c>
+      <c r="R116" s="418">
+        <f>R26</f>
+        <v>20.22625217471897</v>
+      </c>
+      <c r="S116" s="418">
+        <f>S26</f>
+        <v>20.318507233907162</v>
+      </c>
       <c r="T116" s="418">
         <f>T26</f>
         <v>77.16377781143325</v>
@@ -8055,10 +8125,38 @@
           <t>(+) Amortization of intangibles</t>
         </is>
       </c>
+      <c r="L117" s="418">
+        <f>L39</f>
+        <v>8.678750573327381</v>
+      </c>
+      <c r="M117" s="418">
+        <f>M39</f>
+        <v>9.32544481804138</v>
+      </c>
+      <c r="N117" s="418">
+        <f>N39</f>
+        <v>9.449750043187558</v>
+      </c>
       <c r="O117" s="418">
         <f>O39</f>
         <v>36.432945434556316</v>
       </c>
+      <c r="P117" s="418">
+        <f>P39</f>
+        <v>8.940781727637825</v>
+      </c>
+      <c r="Q117" s="418">
+        <f>Q39</f>
+        <v>9.538122574906438</v>
+      </c>
+      <c r="R117" s="418">
+        <f>R39</f>
+        <v>10.206690256533696</v>
+      </c>
+      <c r="S117" s="418">
+        <f>S39</f>
+        <v>10.253244546750103</v>
+      </c>
       <c r="T117" s="418">
         <f>T39</f>
         <v>38.938839105828066</v>
@@ -8082,10 +8180,38 @@
           <t>(+) Share-based compensation</t>
         </is>
       </c>
+      <c r="L118" s="418">
+        <f>L32</f>
+        <v>10.95762459966793</v>
+      </c>
+      <c r="M118" s="418">
+        <f>M32</f>
+        <v>11.774128392981229</v>
+      </c>
+      <c r="N118" s="418">
+        <f>N32</f>
+        <v>11.931073794444336</v>
+      </c>
       <c r="O118" s="418">
         <f>O32</f>
         <v>43.997826787093494</v>
       </c>
+      <c r="P118" s="418">
+        <f>P32</f>
+        <v>11.288460126981704</v>
+      </c>
+      <c r="Q118" s="418">
+        <f>Q32</f>
+        <v>12.042651263956342</v>
+      </c>
+      <c r="R118" s="418">
+        <f>R32</f>
+        <v>12.88677204065624</v>
+      </c>
+      <c r="S118" s="418">
+        <f>S32</f>
+        <v>12.945550597706047</v>
+      </c>
       <c r="T118" s="418">
         <f>T32</f>
         <v>49.16343402930033</v>
@@ -8109,10 +8235,38 @@
           <t>(+) Amortization of debenture discount</t>
         </is>
       </c>
+      <c r="L119" s="418">
+        <f>L29</f>
+        <v>0.0</v>
+      </c>
+      <c r="M119" s="418">
+        <f>M29</f>
+        <v>0.0</v>
+      </c>
+      <c r="N119" s="418">
+        <f>N29</f>
+        <v>0.0</v>
+      </c>
       <c r="O119" s="418">
         <f>O29</f>
         <v>0.0</v>
       </c>
+      <c r="P119" s="418">
+        <f>P29</f>
+        <v>0.0</v>
+      </c>
+      <c r="Q119" s="418">
+        <f>Q29</f>
+        <v>0.0</v>
+      </c>
+      <c r="R119" s="418">
+        <f>R29</f>
+        <v>0.0</v>
+      </c>
+      <c r="S119" s="418">
+        <f>S29</f>
+        <v>0.0</v>
+      </c>
       <c r="T119" s="418">
         <f>T29</f>
         <v>0.0</v>
@@ -8136,10 +8290,38 @@
           <t>(+/-) Decrease / (increase) in net working capital</t>
         </is>
       </c>
+      <c r="L120" s="418">
+        <f>-L87</f>
+        <v>161.453697247994</v>
+      </c>
+      <c r="M120" s="418">
+        <f>-M87</f>
+        <v>31.82667082236162</v>
+      </c>
+      <c r="N120" s="418">
+        <f>-N87</f>
+        <v>-13.487984468144532</v>
+      </c>
       <c r="O120" s="418">
         <f>-O87</f>
         <v>28.013383602211093</v>
       </c>
+      <c r="P120" s="418">
+        <f>-P87</f>
+        <v>0.9740359236727727</v>
+      </c>
+      <c r="Q120" s="418">
+        <f>-Q87</f>
+        <v>55.50048326469391</v>
+      </c>
+      <c r="R120" s="418">
+        <f>-R87</f>
+        <v>30.153452853152203</v>
+      </c>
+      <c r="S120" s="418">
+        <f>-S87</f>
+        <v>-15.892840369892838</v>
+      </c>
       <c r="T120" s="418">
         <f>-T87</f>
         <v>70.73513167162628</v>
@@ -8163,10 +8345,38 @@
           <t>(-) Capital expenditures</t>
         </is>
       </c>
+      <c r="L121" s="418">
+        <f>-L89</f>
+        <v>-20.0</v>
+      </c>
+      <c r="M121" s="418">
+        <f>-M89</f>
+        <v>-20.0</v>
+      </c>
+      <c r="N121" s="418">
+        <f>-N89</f>
+        <v>-20.0</v>
+      </c>
       <c r="O121" s="418">
         <f>-O89</f>
         <v>-80.0</v>
       </c>
+      <c r="P121" s="418">
+        <f>-P89</f>
+        <v>-20.0</v>
+      </c>
+      <c r="Q121" s="418">
+        <f>-Q89</f>
+        <v>-20.0</v>
+      </c>
+      <c r="R121" s="418">
+        <f>-R89</f>
+        <v>-20.0</v>
+      </c>
+      <c r="S121" s="418">
+        <f>-S89</f>
+        <v>-20.0</v>
+      </c>
       <c r="T121" s="418">
         <f>-T89</f>
         <v>-80.0</v>
@@ -8195,10 +8405,38 @@
           <t>$</t>
         </is>
       </c>
+      <c r="L122" s="418">
+        <f>SUM(L115:L121)</f>
+        <v>296.85211249945587</v>
+      </c>
+      <c r="M122" s="418">
+        <f>SUM(M115:M121)</f>
+        <v>178.80454787903432</v>
+      </c>
+      <c r="N122" s="418">
+        <f>SUM(N115:N121)</f>
+        <v>135.71565479150695</v>
+      </c>
       <c r="O122" s="418">
         <f>SUM(O115:O121)</f>
         <v>593.4763151699973</v>
       </c>
+      <c r="P122" s="418">
+        <f>SUM(P115:P121)</f>
+        <v>141.06428161573945</v>
+      </c>
+      <c r="Q122" s="418">
+        <f>SUM(Q115:Q121)</f>
+        <v>206.2864875508366</v>
+      </c>
+      <c r="R122" s="418">
+        <f>SUM(R115:R121)</f>
+        <v>192.91057640760533</v>
+      </c>
+      <c r="S122" s="418">
+        <f>SUM(S115:S121)</f>
+        <v>147.69786664356877</v>
+      </c>
       <c r="T122" s="418">
         <f>SUM(T115:T121)</f>
         <v>695.0768177351315</v>
@@ -8245,10 +8483,38 @@
           <t xml:space="preserve">   FCF margin (% net revenue)</t>
         </is>
       </c>
+      <c r="L124" s="344">
+        <f>L122/L17</f>
+        <v>0.9493254945583147</v>
+      </c>
+      <c r="M124" s="344">
+        <f>M122/M17</f>
+        <v>0.5321587551082835</v>
+      </c>
+      <c r="N124" s="344">
+        <f>N122/N17</f>
+        <v>0.39860416527569326</v>
+      </c>
       <c r="O124" s="344">
         <f>O122/O17</f>
         <v>0.45210708763780955</v>
       </c>
+      <c r="P124" s="344">
+        <f>P122/P17</f>
+        <v>0.4378988213907557</v>
+      </c>
+      <c r="Q124" s="344">
+        <f>Q122/Q17</f>
+        <v>0.6002609471922533</v>
+      </c>
+      <c r="R124" s="344">
+        <f>R122/R17</f>
+        <v>0.5245698318584182</v>
+      </c>
+      <c r="S124" s="344">
+        <f>S122/S17</f>
+        <v>0.3998021395902611</v>
+      </c>
       <c r="T124" s="344">
         <f>T122/T17</f>
         <v>0.49292893634558277</v>
@@ -8277,10 +8543,38 @@
           <t>mm</t>
         </is>
       </c>
+      <c r="L125" s="418">
+        <f>L100</f>
+        <v>397.2806971578966</v>
+      </c>
+      <c r="M125" s="418">
+        <f>M100</f>
+        <v>397.360202332559</v>
+      </c>
+      <c r="N125" s="418">
+        <f>N100</f>
+        <v>397.3999383527922</v>
+      </c>
       <c r="O125" s="418">
         <f>O100</f>
         <v>397.5955894778655</v>
       </c>
+      <c r="P125" s="418">
+        <f>P100</f>
+        <v>397.4396783466275</v>
+      </c>
+      <c r="Q125" s="418">
+        <f>Q100</f>
+        <v>397.4794223144621</v>
+      </c>
+      <c r="R125" s="418">
+        <f>R100</f>
+        <v>397.5191702566935</v>
+      </c>
+      <c r="S125" s="418">
+        <f>S100</f>
+        <v>397.5589221737192</v>
+      </c>
       <c r="T125" s="418">
         <f>T100</f>
         <v>397.4996794120835</v>
@@ -8309,9 +8603,37 @@
           <t>$</t>
         </is>
       </c>
+      <c r="L126" s="419">
+        <f>L122/L125</f>
+        <v>0.7472100069877645</v>
+      </c>
+      <c r="M126" s="419">
+        <f>M122/M125</f>
+        <v>0.4499810167938989</v>
+      </c>
+      <c r="N126" s="419">
+        <f>N122/N125</f>
+        <v>0.34150899809910196</v>
+      </c>
       <c r="O126" s="419">
         <f>O122/O125</f>
         <v>1.4926632258405288</v>
+      </c>
+      <c r="P126" s="419">
+        <f>P122/P125</f>
+        <v>0.3549325578225485</v>
+      </c>
+      <c r="Q126" s="419">
+        <f>Q122/Q125</f>
+        <v>0.5189865838831651</v>
+      </c>
+      <c r="R126" s="419">
+        <f>R122/R125</f>
+        <v>0.48528622225447776</v>
+      </c>
+      <c r="S126" s="419">
+        <f>S122/S125</f>
+        <v>0.3715118902023535</v>
       </c>
       <c r="T126" s="419">
         <f>T122/T125</f>

--- a/EFN_Modelv2.xlsx
+++ b/EFN_Modelv2.xlsx
@@ -19,7 +19,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="10">
+  <numFmts count="11">
     <numFmt numFmtId="164" formatCode="0&quot;A&quot;"/>
     <numFmt numFmtId="165" formatCode="0&quot;E&quot;"/>
     <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
@@ -30,6 +30,7 @@
     <numFmt numFmtId="171" formatCode="[&lt;=9999999]###\-####;###\-###\-####"/>
     <numFmt numFmtId="172" formatCode="0.0%"/>
     <numFmt numFmtId="173" formatCode="0.0\x"/>
+    <numFmt numFmtId="174" formatCode="0.0"/>
   </numFmts>
   <fonts count="37">
     <font>
@@ -499,7 +500,7 @@
     <xf numFmtId="9" fontId="33" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="34" fillId="9" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="420">
+  <cellXfs count="422">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1080,6 +1081,8 @@
     <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="174" fontId="10" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6315,52 +6318,52 @@
         <v>250.255</v>
       </c>
       <c r="L76" s="342">
-        <f>L78*'Revenue Build'!L41</f>
-        <v>247.45152942387315</v>
+        <f>L78*L13/L4</f>
+        <v>265.87768688431726</v>
       </c>
       <c r="M76" s="342">
-        <f>M78*'Revenue Build'!M41</f>
-        <v>255.2202086584112</v>
+        <f>M78*M13/M4</f>
+        <v>272.25356022792045</v>
       </c>
       <c r="N76" s="342">
-        <f>N78*'Revenue Build'!N41</f>
-        <v>251.92788111845923</v>
+        <f>N78*N13/N4</f>
+        <v>274.9120824476124</v>
       </c>
       <c r="O76" s="342">
-        <f>O78*'Revenue Build'!O41</f>
-        <v>251.92788111845923</v>
+        <f>O78*O13/O4</f>
+        <v>267.99863606330814</v>
       </c>
       <c r="P76" s="342">
-        <f>P78*'Revenue Build'!P41</f>
-        <v>252.16563682643655</v>
+        <f>P78*P13/P4</f>
+        <v>281.2973310334358</v>
       </c>
       <c r="Q76" s="342">
-        <f>Q78*'Revenue Build'!Q41</f>
-        <v>265.7129366446227</v>
+        <f>Q78*Q13/Q4</f>
+        <v>293.456334352011</v>
       </c>
       <c r="R76" s="342">
-        <f>R78*'Revenue Build'!R41</f>
-        <v>273.07319447169385</v>
+        <f>R78*R13/R4</f>
+        <v>302.16792565908645</v>
       </c>
       <c r="S76" s="342">
-        <f>S78*'Revenue Build'!S41</f>
-        <v>269.1938575580552</v>
+        <f>S78*S13/S4</f>
+        <v>301.414746718792</v>
       </c>
       <c r="T76" s="342">
-        <f>T78*'Revenue Build'!T41</f>
-        <v>269.19385755805524</v>
+        <f>T78*T13/T4</f>
+        <v>297.46073021757593</v>
       </c>
       <c r="U76" s="342">
-        <f>U78*'Revenue Build'!U41</f>
-        <v>287.6205607080968</v>
+        <f>U78*U13/U4</f>
+        <v>330.14255176358995</v>
       </c>
       <c r="V76" s="342">
-        <f>V78*'Revenue Build'!V41</f>
-        <v>304.27430818079756</v>
+        <f>V78*V13/V4</f>
+        <v>364.7780376968645</v>
       </c>
       <c r="W76" s="342">
-        <f>W78*'Revenue Build'!W41</f>
-        <v>319.7620877847132</v>
+        <f>W78*W13/W4</f>
+        <v>397.94254966297086</v>
       </c>
     </row>
     <row r="77" outlineLevel="1" s="20">
@@ -6404,139 +6407,143 @@
       </c>
       <c r="L77" s="343">
         <f>L76</f>
-        <v>247.45152942387315</v>
+        <v>265.87768688431726</v>
       </c>
       <c r="M77" s="343">
         <f>M76</f>
-        <v>255.2202086584112</v>
+        <v>272.25356022792045</v>
       </c>
       <c r="N77" s="343">
         <f>N76</f>
-        <v>251.92788111845923</v>
+        <v>274.9120824476124</v>
       </c>
       <c r="O77" s="343">
         <f>O76</f>
-        <v>251.92788111845923</v>
+        <v>267.99863606330814</v>
       </c>
       <c r="P77" s="343">
         <f>P76</f>
-        <v>252.16563682643655</v>
+        <v>281.2973310334358</v>
       </c>
       <c r="Q77" s="343">
         <f>Q76</f>
-        <v>265.7129366446227</v>
+        <v>293.456334352011</v>
       </c>
       <c r="R77" s="343">
         <f>R76</f>
-        <v>273.07319447169385</v>
+        <v>302.16792565908645</v>
       </c>
       <c r="S77" s="343">
         <f>S76</f>
-        <v>269.1938575580552</v>
+        <v>301.414746718792</v>
       </c>
       <c r="T77" s="343">
         <f>T76</f>
-        <v>269.19385755805524</v>
+        <v>297.46073021757593</v>
       </c>
       <c r="U77" s="343">
         <f>U76</f>
-        <v>287.6205607080968</v>
+        <v>330.14255176358995</v>
       </c>
       <c r="V77" s="343">
         <f>V76</f>
-        <v>304.27430818079756</v>
+        <v>364.7780376968645</v>
       </c>
       <c r="W77" s="343">
         <f>W76</f>
-        <v>319.7620877847132</v>
+        <v>397.94254966297086</v>
       </c>
     </row>
     <row r="78" outlineLevel="1" ht="5.1" customHeight="1" s="20">
       <c r="B78" s="167" t="inlineStr">
         <is>
-          <t>Accounts receivable - % of Net Earning Assets</t>
+          <t>Accounts receivable - days of service revenue (DSO)</t>
         </is>
       </c>
       <c r="C78" s="72" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E78" s="344">
-        <f>E76/'Revenue Build'!E41</f>
-        <v>0.02730625831000724</v>
-      </c>
-      <c r="F78" s="344">
-        <f>F76/'Revenue Build'!F41</f>
-        <v>0.02443438113764817</v>
-      </c>
-      <c r="G78" s="344">
-        <f>G76/'Revenue Build'!G41</f>
-        <v>0.0299636979481108</v>
-      </c>
-      <c r="H78" s="344">
-        <f>H76/'Revenue Build'!H41</f>
-        <v>0.0242889892706216</v>
-      </c>
-      <c r="I78" s="344">
-        <f>I76/'Revenue Build'!I41</f>
-        <v>0.02767746967691475</v>
-      </c>
-      <c r="J78" s="344">
-        <f>J76/'Revenue Build'!J41</f>
-        <v>0.02767746967691475</v>
-      </c>
-      <c r="K78" s="344">
-        <f>K76/'Revenue Build'!K41</f>
-        <v>0.029652819520964567</v>
-      </c>
-      <c r="L78" s="345">
+          <t>days</t>
+        </is>
+      </c>
+      <c r="D78" s="420">
+        <f>D76/D13*D4</f>
+        <v>147.4179676554993</v>
+      </c>
+      <c r="E78" s="420">
+        <f>E76/E13*E4</f>
+        <v>124.24604224737215</v>
+      </c>
+      <c r="F78" s="420">
+        <f>F76/F13*F4</f>
+        <v>109.27112708385253</v>
+      </c>
+      <c r="G78" s="420">
+        <f>G76/G13*G4</f>
+        <v>149.36805518845483</v>
+      </c>
+      <c r="H78" s="420">
+        <f>H76/H13*H4</f>
+        <v>125.77967599410896</v>
+      </c>
+      <c r="I78" s="420">
+        <f>I76/I13*I4</f>
+        <v>138.4485214657628</v>
+      </c>
+      <c r="J78" s="420">
+        <f>J76/J13*J4</f>
+        <v>143.62617443630268</v>
+      </c>
+      <c r="K78" s="420">
+        <f>K76/K13*K4</f>
+        <v>138.92336160370084</v>
+      </c>
+      <c r="L78" s="421">
         <f>$J$78</f>
-        <v>0.02767746967691475</v>
-      </c>
-      <c r="M78" s="345">
+        <v>143.62617443630268</v>
+      </c>
+      <c r="M78" s="421">
         <f>L78</f>
-        <v>0.02767746967691475</v>
-      </c>
-      <c r="N78" s="345">
+        <v>143.62617443630268</v>
+      </c>
+      <c r="N78" s="421">
         <f>M78</f>
-        <v>0.02767746967691475</v>
-      </c>
-      <c r="O78" s="345">
+        <v>143.62617443630268</v>
+      </c>
+      <c r="O78" s="421">
         <f>N78</f>
-        <v>0.02767746967691475</v>
-      </c>
-      <c r="P78" s="345">
+        <v>143.62617443630268</v>
+      </c>
+      <c r="P78" s="421">
         <f>O78</f>
-        <v>0.02767746967691475</v>
-      </c>
-      <c r="Q78" s="345">
+        <v>143.62617443630268</v>
+      </c>
+      <c r="Q78" s="421">
         <f>P78</f>
-        <v>0.02767746967691475</v>
-      </c>
-      <c r="R78" s="345">
+        <v>143.62617443630268</v>
+      </c>
+      <c r="R78" s="421">
         <f>Q78</f>
-        <v>0.02767746967691475</v>
-      </c>
-      <c r="S78" s="345">
+        <v>143.62617443630268</v>
+      </c>
+      <c r="S78" s="421">
         <f>R78</f>
-        <v>0.02767746967691475</v>
-      </c>
-      <c r="T78" s="345">
+        <v>143.62617443630268</v>
+      </c>
+      <c r="T78" s="421">
         <f>S78</f>
-        <v>0.02767746967691475</v>
-      </c>
-      <c r="U78" s="345">
+        <v>143.62617443630268</v>
+      </c>
+      <c r="U78" s="421">
         <f>T78</f>
-        <v>0.02767746967691475</v>
-      </c>
-      <c r="V78" s="345">
+        <v>143.62617443630268</v>
+      </c>
+      <c r="V78" s="421">
         <f>U78</f>
-        <v>0.02767746967691475</v>
-      </c>
-      <c r="W78" s="345">
+        <v>143.62617443630268</v>
+      </c>
+      <c r="W78" s="421">
         <f>V78</f>
-        <v>0.02767746967691475</v>
+        <v>143.62617443630268</v>
       </c>
     </row>
     <row r="79" outlineLevel="1" s="20">
@@ -6591,52 +6598,52 @@
         <v>1102.559</v>
       </c>
       <c r="L80" s="342">
-        <f>L82*'Revenue Build'!L41</f>
-        <v>1261.209226671867</v>
+        <f>L82*L13/L4</f>
+        <v>1355.123537306064</v>
       </c>
       <c r="M80" s="342">
-        <f>M82*'Revenue Build'!M41</f>
-        <v>1300.8045767287667</v>
+        <f>M82*M13/M4</f>
+        <v>1387.6200440270593</v>
       </c>
       <c r="N80" s="342">
-        <f>N82*'Revenue Build'!N41</f>
-        <v>1284.0242647206703</v>
+        <f>N82*N13/N4</f>
+        <v>1401.1699815061052</v>
       </c>
       <c r="O80" s="342">
-        <f>O82*'Revenue Build'!O41</f>
-        <v>1284.0242647206703</v>
+        <f>O82*O13/O4</f>
+        <v>1365.9335762663134</v>
       </c>
       <c r="P80" s="342">
-        <f>P82*'Revenue Build'!P41</f>
-        <v>1285.2360563523205</v>
+        <f>P82*P13/P4</f>
+        <v>1433.7142718961604</v>
       </c>
       <c r="Q80" s="342">
-        <f>Q82*'Revenue Build'!Q41</f>
-        <v>1354.2838394352004</v>
+        <f>Q82*Q13/Q4</f>
+        <v>1495.6861950773375</v>
       </c>
       <c r="R80" s="342">
-        <f>R82*'Revenue Build'!R41</f>
-        <v>1391.7975501154237</v>
+        <f>R82*R13/R4</f>
+        <v>1540.0873727991266</v>
       </c>
       <c r="S80" s="342">
-        <f>S82*'Revenue Build'!S41</f>
-        <v>1372.0253728318924</v>
+        <f>S82*S13/S4</f>
+        <v>1536.248575637331</v>
       </c>
       <c r="T80" s="342">
-        <f>T82*'Revenue Build'!T41</f>
-        <v>1372.0253728318926</v>
+        <f>T82*T13/T4</f>
+        <v>1516.0957719534858</v>
       </c>
       <c r="U80" s="342">
-        <f>U82*'Revenue Build'!U41</f>
-        <v>1465.942464733018</v>
+        <f>U82*U13/U4</f>
+        <v>1682.668251720506</v>
       </c>
       <c r="V80" s="342">
-        <f>V82*'Revenue Build'!V41</f>
-        <v>1550.8231685223036</v>
+        <f>V82*V13/V4</f>
+        <v>1859.1981544898003</v>
       </c>
       <c r="W80" s="342">
-        <f>W82*'Revenue Build'!W41</f>
-        <v>1629.7611754224713</v>
+        <f>W82*W13/W4</f>
+        <v>2028.2308074182636</v>
       </c>
     </row>
     <row r="81" outlineLevel="1" s="20">
@@ -6680,139 +6687,143 @@
       </c>
       <c r="L81" s="343">
         <f>L80</f>
-        <v>1261.209226671867</v>
+        <v>1355.123537306064</v>
       </c>
       <c r="M81" s="343">
         <f>M80</f>
-        <v>1300.8045767287667</v>
+        <v>1387.6200440270593</v>
       </c>
       <c r="N81" s="343">
         <f>N80</f>
-        <v>1284.0242647206703</v>
+        <v>1401.1699815061052</v>
       </c>
       <c r="O81" s="343">
         <f>O80</f>
-        <v>1284.0242647206703</v>
+        <v>1365.9335762663134</v>
       </c>
       <c r="P81" s="343">
         <f>P80</f>
-        <v>1285.2360563523205</v>
+        <v>1433.7142718961604</v>
       </c>
       <c r="Q81" s="343">
         <f>Q80</f>
-        <v>1354.2838394352004</v>
+        <v>1495.6861950773375</v>
       </c>
       <c r="R81" s="343">
         <f>R80</f>
-        <v>1391.7975501154237</v>
+        <v>1540.0873727991266</v>
       </c>
       <c r="S81" s="343">
         <f>S80</f>
-        <v>1372.0253728318924</v>
+        <v>1536.248575637331</v>
       </c>
       <c r="T81" s="343">
         <f>T80</f>
-        <v>1372.0253728318926</v>
+        <v>1516.0957719534858</v>
       </c>
       <c r="U81" s="343">
         <f>U80</f>
-        <v>1465.942464733018</v>
+        <v>1682.668251720506</v>
       </c>
       <c r="V81" s="343">
         <f>V80</f>
-        <v>1550.8231685223036</v>
+        <v>1859.1981544898003</v>
       </c>
       <c r="W81" s="343">
         <f>W80</f>
-        <v>1629.7611754224713</v>
+        <v>2028.2308074182636</v>
       </c>
     </row>
     <row r="82" outlineLevel="1" s="20">
       <c r="B82" s="167" t="inlineStr">
         <is>
-          <t>Accounts payable - % of Net Earning Assets</t>
+          <t>Accounts payable - days of service revenue (DPO)</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E82" s="344">
-        <f>E80/'Revenue Build'!E41</f>
-        <v>0.18074525738668815</v>
-      </c>
-      <c r="F82" s="344">
-        <f>F80/'Revenue Build'!F41</f>
-        <v>0.16211963491762446</v>
-      </c>
-      <c r="G82" s="344">
-        <f>G80/'Revenue Build'!G41</f>
-        <v>0.16434666861274774</v>
-      </c>
-      <c r="H82" s="344">
-        <f>H80/'Revenue Build'!H41</f>
-        <v>0.1680175654381053</v>
-      </c>
-      <c r="I82" s="344">
-        <f>I80/'Revenue Build'!I41</f>
-        <v>0.1410663341169392</v>
-      </c>
-      <c r="J82" s="344">
-        <f>J80/'Revenue Build'!J41</f>
-        <v>0.1410663341169392</v>
-      </c>
-      <c r="K82" s="344">
-        <f>K80/'Revenue Build'!K41</f>
-        <v>0.13064267662270554</v>
-      </c>
-      <c r="L82" s="345">
+          <t>days</t>
+        </is>
+      </c>
+      <c r="D82" s="420">
+        <f>D80/D13*D4</f>
+        <v>877.7595880097161</v>
+      </c>
+      <c r="E82" s="420">
+        <f>E80/E13*E4</f>
+        <v>822.4079121469592</v>
+      </c>
+      <c r="F82" s="420">
+        <f>F80/F13*F4</f>
+        <v>725.0028200049842</v>
+      </c>
+      <c r="G82" s="420">
+        <f>G80/G13*G4</f>
+        <v>819.2627729026802</v>
+      </c>
+      <c r="H82" s="420">
+        <f>H80/H13*H4</f>
+        <v>870.0730486008837</v>
+      </c>
+      <c r="I82" s="420">
+        <f>I80/I13*I4</f>
+        <v>705.6434571175948</v>
+      </c>
+      <c r="J82" s="420">
+        <f>J80/J13*J4</f>
+        <v>732.0328826109571</v>
+      </c>
+      <c r="K82" s="420">
+        <f>K80/K13*K4</f>
+        <v>612.0605088666152</v>
+      </c>
+      <c r="L82" s="421">
         <f>$J$82</f>
-        <v>0.1410663341169392</v>
-      </c>
-      <c r="M82" s="345">
+        <v>732.0328826109571</v>
+      </c>
+      <c r="M82" s="421">
         <f>L82</f>
-        <v>0.1410663341169392</v>
-      </c>
-      <c r="N82" s="345">
+        <v>732.0328826109571</v>
+      </c>
+      <c r="N82" s="421">
         <f>M82</f>
-        <v>0.1410663341169392</v>
-      </c>
-      <c r="O82" s="345">
+        <v>732.0328826109571</v>
+      </c>
+      <c r="O82" s="421">
         <f>N82</f>
-        <v>0.1410663341169392</v>
-      </c>
-      <c r="P82" s="345">
+        <v>732.0328826109571</v>
+      </c>
+      <c r="P82" s="421">
         <f>O82</f>
-        <v>0.1410663341169392</v>
-      </c>
-      <c r="Q82" s="345">
+        <v>732.0328826109571</v>
+      </c>
+      <c r="Q82" s="421">
         <f>P82</f>
-        <v>0.1410663341169392</v>
-      </c>
-      <c r="R82" s="345">
+        <v>732.0328826109571</v>
+      </c>
+      <c r="R82" s="421">
         <f>Q82</f>
-        <v>0.1410663341169392</v>
-      </c>
-      <c r="S82" s="345">
+        <v>732.0328826109571</v>
+      </c>
+      <c r="S82" s="421">
         <f>R82</f>
-        <v>0.1410663341169392</v>
-      </c>
-      <c r="T82" s="345">
+        <v>732.0328826109571</v>
+      </c>
+      <c r="T82" s="421">
         <f>S82</f>
-        <v>0.1410663341169392</v>
-      </c>
-      <c r="U82" s="345">
+        <v>732.0328826109571</v>
+      </c>
+      <c r="U82" s="421">
         <f>T82</f>
-        <v>0.1410663341169392</v>
-      </c>
-      <c r="V82" s="345">
+        <v>732.0328826109571</v>
+      </c>
+      <c r="V82" s="421">
         <f>U82</f>
-        <v>0.1410663341169392</v>
-      </c>
-      <c r="W82" s="345">
+        <v>732.0328826109571</v>
+      </c>
+      <c r="W82" s="421">
         <f>V82</f>
-        <v>0.1410663341169392</v>
+        <v>732.0328826109571</v>
       </c>
     </row>
     <row r="83" outlineLevel="1" s="20">
@@ -6855,51 +6866,51 @@
       </c>
       <c r="L83" s="346">
         <f>L76-L80</f>
-        <v>-1013.757697247994</v>
+        <v>-1089.2458504217468</v>
       </c>
       <c r="M83" s="346">
         <f>M76-M80</f>
-        <v>-1045.5843680703556</v>
+        <v>-1115.366483799139</v>
       </c>
       <c r="N83" s="346">
         <f>N76-N80</f>
-        <v>-1032.096383602211</v>
+        <v>-1126.2578990584927</v>
       </c>
       <c r="O83" s="346">
         <f>O76-O80</f>
-        <v>-1032.096383602211</v>
+        <v>-1097.9349402030052</v>
       </c>
       <c r="P83" s="346">
         <f>P76-P80</f>
-        <v>-1033.0704195258838</v>
+        <v>-1152.4169408627247</v>
       </c>
       <c r="Q83" s="346">
         <f>Q76-Q80</f>
-        <v>-1088.5709027905777</v>
+        <v>-1202.2298607253265</v>
       </c>
       <c r="R83" s="346">
         <f>R76-R80</f>
-        <v>-1118.72435564373</v>
+        <v>-1237.9194471400401</v>
       </c>
       <c r="S83" s="346">
         <f>S76-S80</f>
-        <v>-1102.831515273837</v>
+        <v>-1234.833828918539</v>
       </c>
       <c r="T83" s="346">
         <f>T76-T80</f>
-        <v>-1102.8315152738373</v>
+        <v>-1218.63504173591</v>
       </c>
       <c r="U83" s="346">
         <f>U76-U80</f>
-        <v>-1178.3219040249212</v>
+        <v>-1352.525699956916</v>
       </c>
       <c r="V83" s="346">
         <f>V76-V80</f>
-        <v>-1246.548860341506</v>
+        <v>-1494.420116792936</v>
       </c>
       <c r="W83" s="346">
         <f>W76-W80</f>
-        <v>-1309.999087637758</v>
+        <v>-1630.2882577552928</v>
       </c>
     </row>
     <row r="84" outlineLevel="1" s="20">
@@ -6930,7 +6941,7 @@
       <c r="N84" s="336" t="n"/>
       <c r="O84" s="335">
         <f>-O83/O13</f>
-        <v>1.5154039015569167</v>
+        <v>1.612073173081245</v>
       </c>
       <c r="P84" s="336" t="n"/>
       <c r="Q84" s="336" t="n"/>
@@ -6938,19 +6949,19 @@
       <c r="S84" s="336" t="n"/>
       <c r="T84" s="335">
         <f>-T83/T13</f>
-        <v>1.458882306280151</v>
+        <v>1.612073173081245</v>
       </c>
       <c r="U84" s="335">
         <f>-U83/U13</f>
-        <v>1.4006026855559928</v>
+        <v>1.6076686015700938</v>
       </c>
       <c r="V84" s="335">
         <f>-V83/V13</f>
-        <v>1.3446874504098891</v>
+        <v>1.6120731730812452</v>
       </c>
       <c r="W84" s="335">
         <f>-W83/W13</f>
-        <v>1.2953625691013972</v>
+        <v>1.6120731730812452</v>
       </c>
     </row>
     <row r="85" outlineLevel="1" ht="5.1" customHeight="1" s="20">
@@ -7019,51 +7030,51 @@
       </c>
       <c r="L87" s="197">
         <f>L83-K83</f>
-        <v>-161.453697247994</v>
+        <v>-236.94185042174684</v>
       </c>
       <c r="M87" s="197">
         <f>M83-L83</f>
-        <v>-31.82667082236162</v>
+        <v>-26.120633377392096</v>
       </c>
       <c r="N87" s="197">
         <f>N83-M83</f>
-        <v>13.487984468144532</v>
+        <v>-10.891415259353835</v>
       </c>
       <c r="O87" s="197">
         <f>O83-J83</f>
-        <v>-28.013383602211093</v>
+        <v>-93.85194020300526</v>
       </c>
       <c r="P87" s="197">
         <f>P83-O83</f>
-        <v>-0.9740359236727727</v>
+        <v>-54.48200065971946</v>
       </c>
       <c r="Q87" s="197">
         <f>Q83-P83</f>
-        <v>-55.50048326469391</v>
+        <v>-49.8129198626018</v>
       </c>
       <c r="R87" s="197">
         <f>R83-Q83</f>
-        <v>-30.153452853152203</v>
+        <v>-35.68958641471363</v>
       </c>
       <c r="S87" s="197">
         <f>S83-R83</f>
-        <v>15.892840369892838</v>
+        <v>3.085618221501136</v>
       </c>
       <c r="T87" s="197">
         <f>T83-O83</f>
-        <v>-70.73513167162628</v>
+        <v>-120.70010153290468</v>
       </c>
       <c r="U87" s="197">
         <f>U83-T83</f>
-        <v>-75.49038875108386</v>
+        <v>-133.8906582210061</v>
       </c>
       <c r="V87" s="197">
         <f>V83-U83</f>
-        <v>-68.22695631658485</v>
+        <v>-141.8944168360199</v>
       </c>
       <c r="W87" s="197">
         <f>W83-V83</f>
-        <v>-63.450227296252024</v>
+        <v>-135.86814096235685</v>
       </c>
       <c r="X87" s="330" t="n"/>
       <c r="Y87" s="330" t="n"/>
@@ -8292,51 +8303,51 @@
       </c>
       <c r="L120" s="418">
         <f>-L87</f>
-        <v>161.453697247994</v>
+        <v>236.94185042174684</v>
       </c>
       <c r="M120" s="418">
         <f>-M87</f>
-        <v>31.82667082236162</v>
+        <v>26.120633377392096</v>
       </c>
       <c r="N120" s="418">
         <f>-N87</f>
-        <v>-13.487984468144532</v>
+        <v>10.891415259353835</v>
       </c>
       <c r="O120" s="418">
         <f>-O87</f>
-        <v>28.013383602211093</v>
+        <v>93.85194020300526</v>
       </c>
       <c r="P120" s="418">
         <f>-P87</f>
-        <v>0.9740359236727727</v>
+        <v>54.48200065971946</v>
       </c>
       <c r="Q120" s="418">
         <f>-Q87</f>
-        <v>55.50048326469391</v>
+        <v>49.8129198626018</v>
       </c>
       <c r="R120" s="418">
         <f>-R87</f>
-        <v>30.153452853152203</v>
+        <v>35.68958641471363</v>
       </c>
       <c r="S120" s="418">
         <f>-S87</f>
-        <v>-15.892840369892838</v>
+        <v>-3.085618221501136</v>
       </c>
       <c r="T120" s="418">
         <f>-T87</f>
-        <v>70.73513167162628</v>
+        <v>120.70010153290468</v>
       </c>
       <c r="U120" s="418">
         <f>-U87</f>
-        <v>75.49038875108386</v>
+        <v>133.8906582210061</v>
       </c>
       <c r="V120" s="418">
         <f>-V87</f>
-        <v>68.22695631658485</v>
+        <v>141.8944168360199</v>
       </c>
       <c r="W120" s="418">
         <f>-W87</f>
-        <v>63.450227296252024</v>
+        <v>135.86814096235685</v>
       </c>
     </row>
     <row r="121">
@@ -8407,51 +8418,51 @@
       </c>
       <c r="L122" s="418">
         <f>SUM(L115:L121)</f>
-        <v>296.85211249945587</v>
+        <v>372.3402656732087</v>
       </c>
       <c r="M122" s="418">
         <f>SUM(M115:M121)</f>
-        <v>178.80454787903432</v>
+        <v>173.0985104340648</v>
       </c>
       <c r="N122" s="418">
         <f>SUM(N115:N121)</f>
-        <v>135.71565479150695</v>
+        <v>160.09505451900532</v>
       </c>
       <c r="O122" s="418">
         <f>SUM(O115:O121)</f>
-        <v>593.4763151699973</v>
+        <v>659.3148717707915</v>
       </c>
       <c r="P122" s="418">
         <f>SUM(P115:P121)</f>
-        <v>141.06428161573945</v>
+        <v>194.57224635178613</v>
       </c>
       <c r="Q122" s="418">
         <f>SUM(Q115:Q121)</f>
-        <v>206.2864875508366</v>
+        <v>200.5989241487445</v>
       </c>
       <c r="R122" s="418">
         <f>SUM(R115:R121)</f>
-        <v>192.91057640760533</v>
+        <v>198.44670996916676</v>
       </c>
       <c r="S122" s="418">
         <f>SUM(S115:S121)</f>
-        <v>147.69786664356877</v>
+        <v>160.50508879196047</v>
       </c>
       <c r="T122" s="418">
         <f>SUM(T115:T121)</f>
-        <v>695.0768177351315</v>
+        <v>745.0417875964099</v>
       </c>
       <c r="U122" s="418">
         <f>SUM(U115:U121)</f>
-        <v>769.557509745625</v>
+        <v>827.9577792155472</v>
       </c>
       <c r="V122" s="418">
         <f>SUM(V115:V121)</f>
-        <v>840.0090199037589</v>
+        <v>913.676480423194</v>
       </c>
       <c r="W122" s="418">
         <f>SUM(W115:W121)</f>
-        <v>907.8432817646716</v>
+        <v>980.2611954307763</v>
       </c>
     </row>
     <row r="123">
@@ -8462,19 +8473,19 @@
       </c>
       <c r="T123" s="344">
         <f>T122/O122-1</f>
-        <v>0.17119554726633268</v>
+        <v>0.13002424106614274</v>
       </c>
       <c r="U123" s="344">
         <f>U122/T122-1</f>
-        <v>0.10715461961914463</v>
+        <v>0.11129039068618396</v>
       </c>
       <c r="V123" s="344">
         <f>V122/U122-1</f>
-        <v>0.09154807700001721</v>
+        <v>0.10353028060061398</v>
       </c>
       <c r="W123" s="344">
         <f>W122/V122-1</f>
-        <v>0.0807542065068354</v>
+        <v>0.0728755926569784</v>
       </c>
     </row>
     <row r="124">
@@ -8485,51 +8496,51 @@
       </c>
       <c r="L124" s="344">
         <f>L122/L17</f>
-        <v>0.9493254945583147</v>
+        <v>1.1907346856251226</v>
       </c>
       <c r="M124" s="344">
         <f>M122/M17</f>
-        <v>0.5321587551082835</v>
+        <v>0.5151764254117787</v>
       </c>
       <c r="N124" s="344">
         <f>N122/N17</f>
-        <v>0.39860416527569326</v>
+        <v>0.47020777130943203</v>
       </c>
       <c r="O124" s="344">
         <f>O122/O17</f>
-        <v>0.45210708763780955</v>
+        <v>0.5022625484678442</v>
       </c>
       <c r="P124" s="344">
         <f>P122/P17</f>
-        <v>0.4378988213907557</v>
+        <v>0.6040009304757432</v>
       </c>
       <c r="Q124" s="344">
         <f>Q122/Q17</f>
-        <v>0.6002609471922533</v>
+        <v>0.5837110401407095</v>
       </c>
       <c r="R124" s="344">
         <f>R122/R17</f>
-        <v>0.5245698318584182</v>
+        <v>0.539623898388176</v>
       </c>
       <c r="S124" s="344">
         <f>S122/S17</f>
-        <v>0.3998021395902611</v>
+        <v>0.4344699038139074</v>
       </c>
       <c r="T124" s="344">
         <f>T122/T17</f>
-        <v>0.49292893634558277</v>
+        <v>0.5283626881552199</v>
       </c>
       <c r="U124" s="344">
         <f>U122/U17</f>
-        <v>0.5024671042595343</v>
+        <v>0.5405983860895667</v>
       </c>
       <c r="V124" s="344">
         <f>V122/V17</f>
-        <v>0.5049238035431176</v>
+        <v>0.5492048213434946</v>
       </c>
       <c r="W124" s="344">
         <f>W122/W17</f>
-        <v>0.5080155921363421</v>
+        <v>0.5485395790747629</v>
       </c>
     </row>
     <row r="125">
@@ -8605,51 +8616,51 @@
       </c>
       <c r="L126" s="419">
         <f>L122/L125</f>
-        <v>0.7472100069877645</v>
+        <v>0.9372221412640759</v>
       </c>
       <c r="M126" s="419">
         <f>M122/M125</f>
-        <v>0.4499810167938989</v>
+        <v>0.43562115535967805</v>
       </c>
       <c r="N126" s="419">
         <f>N122/N125</f>
-        <v>0.34150899809910196</v>
+        <v>0.40285626410158315</v>
       </c>
       <c r="O126" s="419">
         <f>O122/O125</f>
-        <v>1.4926632258405288</v>
+        <v>1.6582549938157605</v>
       </c>
       <c r="P126" s="419">
         <f>P122/P125</f>
-        <v>0.3549325578225485</v>
+        <v>0.48956422056604454</v>
       </c>
       <c r="Q126" s="419">
         <f>Q122/Q125</f>
-        <v>0.5189865838831651</v>
+        <v>0.5046775075315535</v>
       </c>
       <c r="R126" s="419">
         <f>R122/R125</f>
-        <v>0.48528622225447776</v>
+        <v>0.4992129306393502</v>
       </c>
       <c r="S126" s="419">
         <f>S122/S125</f>
-        <v>0.3715118902023535</v>
+        <v>0.40372654175228245</v>
       </c>
       <c r="T126" s="419">
         <f>T122/T125</f>
-        <v>1.7486223354020698</v>
+        <v>1.8743204741658002</v>
       </c>
       <c r="U126" s="419">
         <f>U122/U125</f>
-        <v>1.935610026081336</v>
+        <v>2.08249982402405</v>
       </c>
       <c r="V126" s="419">
         <f>V122/V125</f>
-        <v>2.1128114017910353</v>
+        <v>2.298101615155989</v>
       </c>
       <c r="W126" s="419">
         <f>W122/W125</f>
-        <v>2.283429810041265</v>
+        <v>2.465577132346441</v>
       </c>
     </row>
     <row r="127">
@@ -8660,19 +8671,19 @@
       </c>
       <c r="T127" s="344">
         <f>T126/O126-1</f>
-        <v>0.17147813728539374</v>
+        <v>0.13029689713332804</v>
       </c>
       <c r="U127" s="344">
         <f>U126/T126-1</f>
-        <v>0.10693429158118994</v>
+        <v>0.1110692396138413</v>
       </c>
       <c r="V127" s="344">
         <f>V126/U126-1</f>
-        <v>0.09154807700001721</v>
+        <v>0.10353028060061398</v>
       </c>
       <c r="W127" s="344">
         <f>W126/V126-1</f>
-        <v>0.0807542065068354</v>
+        <v>0.0728755926569784</v>
       </c>
     </row>
     <row r="128">
@@ -8683,23 +8694,23 @@
       </c>
       <c r="O128" s="344">
         <f>O126*O110/O109</f>
-        <v>0.07350564714360913</v>
+        <v>0.0816601523635121</v>
       </c>
       <c r="T128" s="344">
         <f>T126*T110/T109</f>
-        <v>0.08611025859575266</v>
+        <v>0.09230021683591252</v>
       </c>
       <c r="U128" s="344">
         <f>U126*U110/U109</f>
-        <v>0.09531839809656253</v>
+        <v>0.10255193173607</v>
       </c>
       <c r="V128" s="344">
         <f>V126*V110/V109</f>
-        <v>0.10404461414502493</v>
+        <v>0.11316916200484034</v>
       </c>
       <c r="W128" s="344">
         <f>W126*W110/W109</f>
-        <v>0.11244665440161629</v>
+        <v>0.12141643175643665</v>
       </c>
     </row>
   </sheetData>

--- a/EFN_Modelv2.xlsx
+++ b/EFN_Modelv2.xlsx
@@ -32,7 +32,7 @@
     <numFmt numFmtId="173" formatCode="0.0\x"/>
     <numFmt numFmtId="174" formatCode="0.0"/>
   </numFmts>
-  <fonts count="37">
+  <fonts count="38">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -292,6 +292,10 @@
       <color theme="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="11">
     <fill>
@@ -500,7 +504,7 @@
     <xf numFmtId="9" fontId="33" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="34" fillId="9" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="422">
+  <cellXfs count="423">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1083,6 +1087,9 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="174" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="174" fontId="10" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6318,52 +6325,52 @@
         <v>250.255</v>
       </c>
       <c r="L76" s="342">
-        <f>L78*L13/L4</f>
-        <v>265.87768688431726</v>
+        <f>$J$76</f>
+        <v>245.09</v>
       </c>
       <c r="M76" s="342">
-        <f>M78*M13/M4</f>
-        <v>272.25356022792045</v>
+        <f>L76</f>
+        <v>245.09</v>
       </c>
       <c r="N76" s="342">
-        <f>N78*N13/N4</f>
-        <v>274.9120824476124</v>
+        <f>M76</f>
+        <v>245.09</v>
       </c>
       <c r="O76" s="342">
-        <f>O78*O13/O4</f>
-        <v>267.99863606330814</v>
+        <f>N76</f>
+        <v>245.09</v>
       </c>
       <c r="P76" s="342">
-        <f>P78*P13/P4</f>
-        <v>281.2973310334358</v>
+        <f>O76</f>
+        <v>245.09</v>
       </c>
       <c r="Q76" s="342">
-        <f>Q78*Q13/Q4</f>
-        <v>293.456334352011</v>
+        <f>P76</f>
+        <v>245.09</v>
       </c>
       <c r="R76" s="342">
-        <f>R78*R13/R4</f>
-        <v>302.16792565908645</v>
+        <f>Q76</f>
+        <v>245.09</v>
       </c>
       <c r="S76" s="342">
-        <f>S78*S13/S4</f>
-        <v>301.414746718792</v>
+        <f>R76</f>
+        <v>245.09</v>
       </c>
       <c r="T76" s="342">
-        <f>T78*T13/T4</f>
-        <v>297.46073021757593</v>
+        <f>S76</f>
+        <v>245.09</v>
       </c>
       <c r="U76" s="342">
-        <f>U78*U13/U4</f>
-        <v>330.14255176358995</v>
+        <f>T76</f>
+        <v>245.09</v>
       </c>
       <c r="V76" s="342">
-        <f>V78*V13/V4</f>
-        <v>364.7780376968645</v>
+        <f>U76</f>
+        <v>245.09</v>
       </c>
       <c r="W76" s="342">
-        <f>W78*W13/W4</f>
-        <v>397.94254966297086</v>
+        <f>V76</f>
+        <v>245.09</v>
       </c>
     </row>
     <row r="77" outlineLevel="1" s="20">
@@ -6407,144 +6414,80 @@
       </c>
       <c r="L77" s="343">
         <f>L76</f>
-        <v>265.87768688431726</v>
+        <v>245.09</v>
       </c>
       <c r="M77" s="343">
         <f>M76</f>
-        <v>272.25356022792045</v>
+        <v>245.09</v>
       </c>
       <c r="N77" s="343">
         <f>N76</f>
-        <v>274.9120824476124</v>
+        <v>245.09</v>
       </c>
       <c r="O77" s="343">
         <f>O76</f>
-        <v>267.99863606330814</v>
+        <v>245.09</v>
       </c>
       <c r="P77" s="343">
         <f>P76</f>
-        <v>281.2973310334358</v>
+        <v>245.09</v>
       </c>
       <c r="Q77" s="343">
         <f>Q76</f>
-        <v>293.456334352011</v>
+        <v>245.09</v>
       </c>
       <c r="R77" s="343">
         <f>R76</f>
-        <v>302.16792565908645</v>
+        <v>245.09</v>
       </c>
       <c r="S77" s="343">
         <f>S76</f>
-        <v>301.414746718792</v>
+        <v>245.09</v>
       </c>
       <c r="T77" s="343">
         <f>T76</f>
-        <v>297.46073021757593</v>
+        <v>245.09</v>
       </c>
       <c r="U77" s="343">
         <f>U76</f>
-        <v>330.14255176358995</v>
+        <v>245.09</v>
       </c>
       <c r="V77" s="343">
         <f>V76</f>
-        <v>364.7780376968645</v>
+        <v>245.09</v>
       </c>
       <c r="W77" s="343">
         <f>W76</f>
-        <v>397.94254966297086</v>
+        <v>245.09</v>
       </c>
     </row>
     <row r="78" outlineLevel="1" ht="5.1" customHeight="1" s="20">
-      <c r="B78" s="167" t="inlineStr">
-        <is>
-          <t>Accounts receivable - days of service revenue (DSO)</t>
-        </is>
-      </c>
-      <c r="C78" s="72" t="inlineStr">
-        <is>
-          <t>days</t>
-        </is>
-      </c>
-      <c r="D78" s="420">
-        <f>D76/D13*D4</f>
-        <v>147.4179676554993</v>
-      </c>
-      <c r="E78" s="420">
-        <f>E76/E13*E4</f>
-        <v>124.24604224737215</v>
-      </c>
-      <c r="F78" s="420">
-        <f>F76/F13*F4</f>
-        <v>109.27112708385253</v>
-      </c>
-      <c r="G78" s="420">
-        <f>G76/G13*G4</f>
-        <v>149.36805518845483</v>
-      </c>
-      <c r="H78" s="420">
-        <f>H76/H13*H4</f>
-        <v>125.77967599410896</v>
-      </c>
-      <c r="I78" s="420">
-        <f>I76/I13*I4</f>
-        <v>138.4485214657628</v>
-      </c>
-      <c r="J78" s="420">
-        <f>J76/J13*J4</f>
-        <v>143.62617443630268</v>
-      </c>
-      <c r="K78" s="420">
-        <f>K76/K13*K4</f>
-        <v>138.92336160370084</v>
-      </c>
-      <c r="L78" s="421">
-        <f>$J$78</f>
-        <v>143.62617443630268</v>
-      </c>
-      <c r="M78" s="421">
-        <f>L78</f>
-        <v>143.62617443630268</v>
-      </c>
-      <c r="N78" s="421">
-        <f>M78</f>
-        <v>143.62617443630268</v>
-      </c>
-      <c r="O78" s="421">
-        <f>N78</f>
-        <v>143.62617443630268</v>
-      </c>
-      <c r="P78" s="421">
-        <f>O78</f>
-        <v>143.62617443630268</v>
-      </c>
-      <c r="Q78" s="421">
-        <f>P78</f>
-        <v>143.62617443630268</v>
-      </c>
-      <c r="R78" s="421">
-        <f>Q78</f>
-        <v>143.62617443630268</v>
-      </c>
-      <c r="S78" s="421">
-        <f>R78</f>
-        <v>143.62617443630268</v>
-      </c>
-      <c r="T78" s="421">
-        <f>S78</f>
-        <v>143.62617443630268</v>
-      </c>
-      <c r="U78" s="421">
-        <f>T78</f>
-        <v>143.62617443630268</v>
-      </c>
-      <c r="V78" s="421">
-        <f>U78</f>
-        <v>143.62617443630268</v>
-      </c>
-      <c r="W78" s="421">
-        <f>V78</f>
-        <v>143.62617443630268</v>
-      </c>
+      <c r="B78" s="422" t="inlineStr">
+        <is>
+          <t>Receivables &amp; payables held flat at FY2025 normalized level (working-capital neutral)</t>
+        </is>
+      </c>
+      <c r="C78" s="72" t="n"/>
+      <c r="D78" s="420" t="n"/>
+      <c r="E78" s="420" t="n"/>
+      <c r="F78" s="420" t="n"/>
+      <c r="G78" s="420" t="n"/>
+      <c r="H78" s="420" t="n"/>
+      <c r="I78" s="420" t="n"/>
+      <c r="J78" s="420" t="n"/>
+      <c r="K78" s="420" t="n"/>
+      <c r="L78" s="421" t="n"/>
+      <c r="M78" s="421" t="n"/>
+      <c r="N78" s="421" t="n"/>
+      <c r="O78" s="421" t="n"/>
+      <c r="P78" s="421" t="n"/>
+      <c r="Q78" s="421" t="n"/>
+      <c r="R78" s="421" t="n"/>
+      <c r="S78" s="421" t="n"/>
+      <c r="T78" s="421" t="n"/>
+      <c r="U78" s="421" t="n"/>
+      <c r="V78" s="421" t="n"/>
+      <c r="W78" s="421" t="n"/>
     </row>
     <row r="79" outlineLevel="1" s="20">
       <c r="B79" s="298" t="inlineStr">
@@ -6598,52 +6541,52 @@
         <v>1102.559</v>
       </c>
       <c r="L80" s="342">
-        <f>L82*L13/L4</f>
-        <v>1355.123537306064</v>
+        <f>$J$80</f>
+        <v>1249.173</v>
       </c>
       <c r="M80" s="342">
-        <f>M82*M13/M4</f>
-        <v>1387.6200440270593</v>
+        <f>L80</f>
+        <v>1249.173</v>
       </c>
       <c r="N80" s="342">
-        <f>N82*N13/N4</f>
-        <v>1401.1699815061052</v>
+        <f>M80</f>
+        <v>1249.173</v>
       </c>
       <c r="O80" s="342">
-        <f>O82*O13/O4</f>
-        <v>1365.9335762663134</v>
+        <f>N80</f>
+        <v>1249.173</v>
       </c>
       <c r="P80" s="342">
-        <f>P82*P13/P4</f>
-        <v>1433.7142718961604</v>
+        <f>O80</f>
+        <v>1249.173</v>
       </c>
       <c r="Q80" s="342">
-        <f>Q82*Q13/Q4</f>
-        <v>1495.6861950773375</v>
+        <f>P80</f>
+        <v>1249.173</v>
       </c>
       <c r="R80" s="342">
-        <f>R82*R13/R4</f>
-        <v>1540.0873727991266</v>
+        <f>Q80</f>
+        <v>1249.173</v>
       </c>
       <c r="S80" s="342">
-        <f>S82*S13/S4</f>
-        <v>1536.248575637331</v>
+        <f>R80</f>
+        <v>1249.173</v>
       </c>
       <c r="T80" s="342">
-        <f>T82*T13/T4</f>
-        <v>1516.0957719534858</v>
+        <f>S80</f>
+        <v>1249.173</v>
       </c>
       <c r="U80" s="342">
-        <f>U82*U13/U4</f>
-        <v>1682.668251720506</v>
+        <f>T80</f>
+        <v>1249.173</v>
       </c>
       <c r="V80" s="342">
-        <f>V82*V13/V4</f>
-        <v>1859.1981544898003</v>
+        <f>U80</f>
+        <v>1249.173</v>
       </c>
       <c r="W80" s="342">
-        <f>W82*W13/W4</f>
-        <v>2028.2308074182636</v>
+        <f>V80</f>
+        <v>1249.173</v>
       </c>
     </row>
     <row r="81" outlineLevel="1" s="20">
@@ -6687,144 +6630,76 @@
       </c>
       <c r="L81" s="343">
         <f>L80</f>
-        <v>1355.123537306064</v>
+        <v>1249.173</v>
       </c>
       <c r="M81" s="343">
         <f>M80</f>
-        <v>1387.6200440270593</v>
+        <v>1249.173</v>
       </c>
       <c r="N81" s="343">
         <f>N80</f>
-        <v>1401.1699815061052</v>
+        <v>1249.173</v>
       </c>
       <c r="O81" s="343">
         <f>O80</f>
-        <v>1365.9335762663134</v>
+        <v>1249.173</v>
       </c>
       <c r="P81" s="343">
         <f>P80</f>
-        <v>1433.7142718961604</v>
+        <v>1249.173</v>
       </c>
       <c r="Q81" s="343">
         <f>Q80</f>
-        <v>1495.6861950773375</v>
+        <v>1249.173</v>
       </c>
       <c r="R81" s="343">
         <f>R80</f>
-        <v>1540.0873727991266</v>
+        <v>1249.173</v>
       </c>
       <c r="S81" s="343">
         <f>S80</f>
-        <v>1536.248575637331</v>
+        <v>1249.173</v>
       </c>
       <c r="T81" s="343">
         <f>T80</f>
-        <v>1516.0957719534858</v>
+        <v>1249.173</v>
       </c>
       <c r="U81" s="343">
         <f>U80</f>
-        <v>1682.668251720506</v>
+        <v>1249.173</v>
       </c>
       <c r="V81" s="343">
         <f>V80</f>
-        <v>1859.1981544898003</v>
+        <v>1249.173</v>
       </c>
       <c r="W81" s="343">
         <f>W80</f>
-        <v>2028.2308074182636</v>
+        <v>1249.173</v>
       </c>
     </row>
     <row r="82" outlineLevel="1" s="20">
-      <c r="B82" s="167" t="inlineStr">
-        <is>
-          <t>Accounts payable - days of service revenue (DPO)</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>days</t>
-        </is>
-      </c>
-      <c r="D82" s="420">
-        <f>D80/D13*D4</f>
-        <v>877.7595880097161</v>
-      </c>
-      <c r="E82" s="420">
-        <f>E80/E13*E4</f>
-        <v>822.4079121469592</v>
-      </c>
-      <c r="F82" s="420">
-        <f>F80/F13*F4</f>
-        <v>725.0028200049842</v>
-      </c>
-      <c r="G82" s="420">
-        <f>G80/G13*G4</f>
-        <v>819.2627729026802</v>
-      </c>
-      <c r="H82" s="420">
-        <f>H80/H13*H4</f>
-        <v>870.0730486008837</v>
-      </c>
-      <c r="I82" s="420">
-        <f>I80/I13*I4</f>
-        <v>705.6434571175948</v>
-      </c>
-      <c r="J82" s="420">
-        <f>J80/J13*J4</f>
-        <v>732.0328826109571</v>
-      </c>
-      <c r="K82" s="420">
-        <f>K80/K13*K4</f>
-        <v>612.0605088666152</v>
-      </c>
-      <c r="L82" s="421">
-        <f>$J$82</f>
-        <v>732.0328826109571</v>
-      </c>
-      <c r="M82" s="421">
-        <f>L82</f>
-        <v>732.0328826109571</v>
-      </c>
-      <c r="N82" s="421">
-        <f>M82</f>
-        <v>732.0328826109571</v>
-      </c>
-      <c r="O82" s="421">
-        <f>N82</f>
-        <v>732.0328826109571</v>
-      </c>
-      <c r="P82" s="421">
-        <f>O82</f>
-        <v>732.0328826109571</v>
-      </c>
-      <c r="Q82" s="421">
-        <f>P82</f>
-        <v>732.0328826109571</v>
-      </c>
-      <c r="R82" s="421">
-        <f>Q82</f>
-        <v>732.0328826109571</v>
-      </c>
-      <c r="S82" s="421">
-        <f>R82</f>
-        <v>732.0328826109571</v>
-      </c>
-      <c r="T82" s="421">
-        <f>S82</f>
-        <v>732.0328826109571</v>
-      </c>
-      <c r="U82" s="421">
-        <f>T82</f>
-        <v>732.0328826109571</v>
-      </c>
-      <c r="V82" s="421">
-        <f>U82</f>
-        <v>732.0328826109571</v>
-      </c>
-      <c r="W82" s="421">
-        <f>V82</f>
-        <v>732.0328826109571</v>
-      </c>
+      <c r="B82" s="167" t="n"/>
+      <c r="C82" s="2" t="n"/>
+      <c r="D82" s="420" t="n"/>
+      <c r="E82" s="420" t="n"/>
+      <c r="F82" s="420" t="n"/>
+      <c r="G82" s="420" t="n"/>
+      <c r="H82" s="420" t="n"/>
+      <c r="I82" s="420" t="n"/>
+      <c r="J82" s="420" t="n"/>
+      <c r="K82" s="420" t="n"/>
+      <c r="L82" s="421" t="n"/>
+      <c r="M82" s="421" t="n"/>
+      <c r="N82" s="421" t="n"/>
+      <c r="O82" s="421" t="n"/>
+      <c r="P82" s="421" t="n"/>
+      <c r="Q82" s="421" t="n"/>
+      <c r="R82" s="421" t="n"/>
+      <c r="S82" s="421" t="n"/>
+      <c r="T82" s="421" t="n"/>
+      <c r="U82" s="421" t="n"/>
+      <c r="V82" s="421" t="n"/>
+      <c r="W82" s="421" t="n"/>
     </row>
     <row r="83" outlineLevel="1" s="20">
       <c r="B83" s="307" t="inlineStr">
@@ -6866,51 +6741,51 @@
       </c>
       <c r="L83" s="346">
         <f>L76-L80</f>
-        <v>-1089.2458504217468</v>
+        <v>-1004.083</v>
       </c>
       <c r="M83" s="346">
         <f>M76-M80</f>
-        <v>-1115.366483799139</v>
+        <v>-1004.083</v>
       </c>
       <c r="N83" s="346">
         <f>N76-N80</f>
-        <v>-1126.2578990584927</v>
+        <v>-1004.083</v>
       </c>
       <c r="O83" s="346">
         <f>O76-O80</f>
-        <v>-1097.9349402030052</v>
+        <v>-1004.083</v>
       </c>
       <c r="P83" s="346">
         <f>P76-P80</f>
-        <v>-1152.4169408627247</v>
+        <v>-1004.083</v>
       </c>
       <c r="Q83" s="346">
         <f>Q76-Q80</f>
-        <v>-1202.2298607253265</v>
+        <v>-1004.083</v>
       </c>
       <c r="R83" s="346">
         <f>R76-R80</f>
-        <v>-1237.9194471400401</v>
+        <v>-1004.083</v>
       </c>
       <c r="S83" s="346">
         <f>S76-S80</f>
-        <v>-1234.833828918539</v>
+        <v>-1004.083</v>
       </c>
       <c r="T83" s="346">
         <f>T76-T80</f>
-        <v>-1218.63504173591</v>
+        <v>-1004.083</v>
       </c>
       <c r="U83" s="346">
         <f>U76-U80</f>
-        <v>-1352.525699956916</v>
+        <v>-1004.083</v>
       </c>
       <c r="V83" s="346">
         <f>V76-V80</f>
-        <v>-1494.420116792936</v>
+        <v>-1004.083</v>
       </c>
       <c r="W83" s="346">
         <f>W76-W80</f>
-        <v>-1630.2882577552928</v>
+        <v>-1004.083</v>
       </c>
     </row>
     <row r="84" outlineLevel="1" s="20">
@@ -6941,7 +6816,7 @@
       <c r="N84" s="336" t="n"/>
       <c r="O84" s="335">
         <f>-O83/O13</f>
-        <v>1.612073173081245</v>
+        <v>1.4742724806149723</v>
       </c>
       <c r="P84" s="336" t="n"/>
       <c r="Q84" s="336" t="n"/>
@@ -6949,19 +6824,19 @@
       <c r="S84" s="336" t="n"/>
       <c r="T84" s="335">
         <f>-T83/T13</f>
-        <v>1.612073173081245</v>
+        <v>1.3282526863343833</v>
       </c>
       <c r="U84" s="335">
         <f>-U83/U13</f>
-        <v>1.6076686015700938</v>
+        <v>1.193495038594627</v>
       </c>
       <c r="V84" s="335">
         <f>-V83/V13</f>
-        <v>1.6120731730812452</v>
+        <v>1.0831326811369562</v>
       </c>
       <c r="W84" s="335">
         <f>-W83/W13</f>
-        <v>1.6120731730812452</v>
+        <v>0.9928644582618941</v>
       </c>
     </row>
     <row r="85" outlineLevel="1" ht="5.1" customHeight="1" s="20">
@@ -7030,51 +6905,51 @@
       </c>
       <c r="L87" s="197">
         <f>L83-K83</f>
-        <v>-236.94185042174684</v>
+        <v>-151.779</v>
       </c>
       <c r="M87" s="197">
         <f>M83-L83</f>
-        <v>-26.120633377392096</v>
+        <v>0.0</v>
       </c>
       <c r="N87" s="197">
         <f>N83-M83</f>
-        <v>-10.891415259353835</v>
+        <v>0.0</v>
       </c>
       <c r="O87" s="197">
         <f>O83-J83</f>
-        <v>-93.85194020300526</v>
+        <v>0.0</v>
       </c>
       <c r="P87" s="197">
         <f>P83-O83</f>
-        <v>-54.48200065971946</v>
+        <v>0.0</v>
       </c>
       <c r="Q87" s="197">
         <f>Q83-P83</f>
-        <v>-49.8129198626018</v>
+        <v>0.0</v>
       </c>
       <c r="R87" s="197">
         <f>R83-Q83</f>
-        <v>-35.68958641471363</v>
+        <v>0.0</v>
       </c>
       <c r="S87" s="197">
         <f>S83-R83</f>
-        <v>3.085618221501136</v>
+        <v>0.0</v>
       </c>
       <c r="T87" s="197">
         <f>T83-O83</f>
-        <v>-120.70010153290468</v>
+        <v>0.0</v>
       </c>
       <c r="U87" s="197">
         <f>U83-T83</f>
-        <v>-133.8906582210061</v>
+        <v>0.0</v>
       </c>
       <c r="V87" s="197">
         <f>V83-U83</f>
-        <v>-141.8944168360199</v>
+        <v>0.0</v>
       </c>
       <c r="W87" s="197">
         <f>W83-V83</f>
-        <v>-135.86814096235685</v>
+        <v>0.0</v>
       </c>
       <c r="X87" s="330" t="n"/>
       <c r="Y87" s="330" t="n"/>
@@ -8303,51 +8178,51 @@
       </c>
       <c r="L120" s="418">
         <f>-L87</f>
-        <v>236.94185042174684</v>
+        <v>151.779</v>
       </c>
       <c r="M120" s="418">
         <f>-M87</f>
-        <v>26.120633377392096</v>
+        <v>-0.0</v>
       </c>
       <c r="N120" s="418">
         <f>-N87</f>
-        <v>10.891415259353835</v>
+        <v>-0.0</v>
       </c>
       <c r="O120" s="418">
         <f>-O87</f>
-        <v>93.85194020300526</v>
+        <v>-0.0</v>
       </c>
       <c r="P120" s="418">
         <f>-P87</f>
-        <v>54.48200065971946</v>
+        <v>-0.0</v>
       </c>
       <c r="Q120" s="418">
         <f>-Q87</f>
-        <v>49.8129198626018</v>
+        <v>-0.0</v>
       </c>
       <c r="R120" s="418">
         <f>-R87</f>
-        <v>35.68958641471363</v>
+        <v>-0.0</v>
       </c>
       <c r="S120" s="418">
         <f>-S87</f>
-        <v>-3.085618221501136</v>
+        <v>-0.0</v>
       </c>
       <c r="T120" s="418">
         <f>-T87</f>
-        <v>120.70010153290468</v>
+        <v>-0.0</v>
       </c>
       <c r="U120" s="418">
         <f>-U87</f>
-        <v>133.8906582210061</v>
+        <v>-0.0</v>
       </c>
       <c r="V120" s="418">
         <f>-V87</f>
-        <v>141.8944168360199</v>
+        <v>-0.0</v>
       </c>
       <c r="W120" s="418">
         <f>-W87</f>
-        <v>135.86814096235685</v>
+        <v>-0.0</v>
       </c>
     </row>
     <row r="121">
@@ -8418,51 +8293,51 @@
       </c>
       <c r="L122" s="418">
         <f>SUM(L115:L121)</f>
-        <v>372.3402656732087</v>
+        <v>287.17741525146187</v>
       </c>
       <c r="M122" s="418">
         <f>SUM(M115:M121)</f>
-        <v>173.0985104340648</v>
+        <v>146.9778770566727</v>
       </c>
       <c r="N122" s="418">
         <f>SUM(N115:N121)</f>
-        <v>160.09505451900532</v>
+        <v>149.20363925965148</v>
       </c>
       <c r="O122" s="418">
         <f>SUM(O115:O121)</f>
-        <v>659.3148717707915</v>
+        <v>565.4629315677862</v>
       </c>
       <c r="P122" s="418">
         <f>SUM(P115:P121)</f>
-        <v>194.57224635178613</v>
+        <v>140.09024569206667</v>
       </c>
       <c r="Q122" s="418">
         <f>SUM(Q115:Q121)</f>
-        <v>200.5989241487445</v>
+        <v>150.78600428614268</v>
       </c>
       <c r="R122" s="418">
         <f>SUM(R115:R121)</f>
-        <v>198.44670996916676</v>
+        <v>162.75712355445313</v>
       </c>
       <c r="S122" s="418">
         <f>SUM(S115:S121)</f>
-        <v>160.50508879196047</v>
+        <v>163.5907070134616</v>
       </c>
       <c r="T122" s="418">
         <f>SUM(T115:T121)</f>
-        <v>745.0417875964099</v>
+        <v>624.3416860635052</v>
       </c>
       <c r="U122" s="418">
         <f>SUM(U115:U121)</f>
-        <v>827.9577792155472</v>
+        <v>694.0671209945411</v>
       </c>
       <c r="V122" s="418">
         <f>SUM(V115:V121)</f>
-        <v>913.676480423194</v>
+        <v>771.7820635871741</v>
       </c>
       <c r="W122" s="418">
         <f>SUM(W115:W121)</f>
-        <v>980.2611954307763</v>
+        <v>844.3930544684196</v>
       </c>
     </row>
     <row r="123">
@@ -8473,19 +8348,19 @@
       </c>
       <c r="T123" s="344">
         <f>T122/O122-1</f>
-        <v>0.13002424106614274</v>
+        <v>0.10412487045344165</v>
       </c>
       <c r="U123" s="344">
         <f>U122/T122-1</f>
-        <v>0.11129039068618396</v>
+        <v>0.11167832692809143</v>
       </c>
       <c r="V123" s="344">
         <f>V122/U122-1</f>
-        <v>0.10353028060061398</v>
+        <v>0.1119703559524241</v>
       </c>
       <c r="W123" s="344">
         <f>W122/V122-1</f>
-        <v>0.0728755926569784</v>
+        <v>0.09408224718744562</v>
       </c>
     </row>
     <row r="124">
@@ -8496,51 +8371,51 @@
       </c>
       <c r="L124" s="344">
         <f>L122/L17</f>
-        <v>1.1907346856251226</v>
+        <v>0.9183860591865327</v>
       </c>
       <c r="M124" s="344">
         <f>M122/M17</f>
-        <v>0.5151764254117787</v>
+        <v>0.43743609998025346</v>
       </c>
       <c r="N124" s="344">
         <f>N122/N17</f>
-        <v>0.47020777130943203</v>
+        <v>0.4382190998861161</v>
       </c>
       <c r="O124" s="344">
         <f>O122/O17</f>
-        <v>0.5022625484678442</v>
+        <v>0.4307666416056059</v>
       </c>
       <c r="P124" s="344">
         <f>P122/P17</f>
-        <v>0.6040009304757432</v>
+        <v>0.4348751702007937</v>
       </c>
       <c r="Q124" s="344">
         <f>Q122/Q17</f>
-        <v>0.5837110401407095</v>
+        <v>0.4387633471815741</v>
       </c>
       <c r="R124" s="344">
         <f>R122/R17</f>
-        <v>0.539623898388176</v>
+        <v>0.44257540735518397</v>
       </c>
       <c r="S124" s="344">
         <f>S122/S17</f>
-        <v>0.4344699038139074</v>
+        <v>0.4428223383815096</v>
       </c>
       <c r="T124" s="344">
         <f>T122/T17</f>
-        <v>0.5283626881552199</v>
+        <v>0.4427655697542858</v>
       </c>
       <c r="U124" s="344">
         <f>U122/U17</f>
-        <v>0.5405983860895667</v>
+        <v>0.4531771726367219</v>
       </c>
       <c r="V124" s="344">
         <f>V122/V17</f>
-        <v>0.5492048213434946</v>
+        <v>0.4639130364307751</v>
       </c>
       <c r="W124" s="344">
         <f>W122/W17</f>
-        <v>0.5485395790747629</v>
+        <v>0.4725097890549612</v>
       </c>
     </row>
     <row r="125">
@@ -8616,51 +8491,51 @@
       </c>
       <c r="L126" s="419">
         <f>L122/L125</f>
-        <v>0.9372221412640759</v>
+        <v>0.722857710696488</v>
       </c>
       <c r="M126" s="419">
         <f>M122/M125</f>
-        <v>0.43562115535967805</v>
+        <v>0.3698857515017668</v>
       </c>
       <c r="N126" s="419">
         <f>N122/N125</f>
-        <v>0.40285626410158315</v>
+        <v>0.3754495782714385</v>
       </c>
       <c r="O126" s="419">
         <f>O122/O125</f>
-        <v>1.6582549938157605</v>
+        <v>1.4222062480883382</v>
       </c>
       <c r="P126" s="419">
         <f>P122/P125</f>
-        <v>0.48956422056604454</v>
+        <v>0.35248178107140776</v>
       </c>
       <c r="Q126" s="419">
         <f>Q122/Q125</f>
-        <v>0.5046775075315535</v>
+        <v>0.3793554982246345</v>
       </c>
       <c r="R126" s="419">
         <f>R122/R125</f>
-        <v>0.4992129306393502</v>
+        <v>0.40943213744724455</v>
       </c>
       <c r="S126" s="419">
         <f>S122/S125</f>
-        <v>0.40372654175228245</v>
+        <v>0.41148795282722456</v>
       </c>
       <c r="T126" s="419">
         <f>T122/T125</f>
-        <v>1.8743204741658002</v>
+        <v>1.5706721750994348</v>
       </c>
       <c r="U126" s="419">
         <f>U122/U125</f>
-        <v>2.08249982402405</v>
+        <v>1.7457347386740634</v>
       </c>
       <c r="V126" s="419">
         <f>V122/V125</f>
-        <v>2.298101615155989</v>
+        <v>1.94120527876191</v>
       </c>
       <c r="W126" s="419">
         <f>W122/W125</f>
-        <v>2.465577132346441</v>
+        <v>2.1238382336399626</v>
       </c>
     </row>
     <row r="127">
@@ -8671,19 +8546,19 @@
       </c>
       <c r="T127" s="344">
         <f>T126/O126-1</f>
-        <v>0.13029689713332804</v>
+        <v>0.1043912774329725</v>
       </c>
       <c r="U127" s="344">
         <f>U126/T126-1</f>
-        <v>0.1110692396138413</v>
+        <v>0.11145709865494102</v>
       </c>
       <c r="V127" s="344">
         <f>V126/U126-1</f>
-        <v>0.10353028060061398</v>
+        <v>0.11197035595242388</v>
       </c>
       <c r="W127" s="344">
         <f>W126/V126-1</f>
-        <v>0.0728755926569784</v>
+        <v>0.09408224718744584</v>
       </c>
     </row>
     <row r="128">
@@ -8694,23 +8569,23 @@
       </c>
       <c r="O128" s="344">
         <f>O126*O110/O109</f>
-        <v>0.0816601523635121</v>
+        <v>0.07003601939650542</v>
       </c>
       <c r="T128" s="344">
         <f>T126*T110/T109</f>
-        <v>0.09230021683591252</v>
+        <v>0.07734716892762705</v>
       </c>
       <c r="U128" s="344">
         <f>U126*U110/U109</f>
-        <v>0.10255193173607</v>
+        <v>0.08596805996547398</v>
       </c>
       <c r="V128" s="344">
         <f>V126*V110/V109</f>
-        <v>0.11316916200484034</v>
+        <v>0.09559393424034743</v>
       </c>
       <c r="W128" s="344">
         <f>W126*W110/W109</f>
-        <v>0.12141643175643665</v>
+        <v>0.10458762639116823</v>
       </c>
     </row>
   </sheetData>

--- a/EFN_Modelv2.xlsx
+++ b/EFN_Modelv2.xlsx
@@ -19,7 +19,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="11">
+  <numFmts count="12">
     <numFmt numFmtId="164" formatCode="0&quot;A&quot;"/>
     <numFmt numFmtId="165" formatCode="0&quot;E&quot;"/>
     <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
@@ -31,6 +31,7 @@
     <numFmt numFmtId="172" formatCode="0.0%"/>
     <numFmt numFmtId="173" formatCode="0.0\x"/>
     <numFmt numFmtId="174" formatCode="0.0"/>
+    <numFmt numFmtId="175" formatCode="0.000"/>
   </numFmts>
   <fonts count="38">
     <font>
@@ -504,7 +505,7 @@
     <xf numFmtId="9" fontId="33" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="34" fillId="9" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="423">
+  <cellXfs count="425">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1090,6 +1091,8 @@
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1596,7 +1599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB128"/>
+  <dimension ref="A1:AB156"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col width="10.5703125" customWidth="1" style="305" min="1" max="1"/>
@@ -8586,6 +8589,338 @@
       <c r="W128" s="344">
         <f>W126*W110/W109</f>
         <v>0.10458762639116823</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" s="82" t="inlineStr">
+        <is>
+          <t>Dividend Discount Model (DDM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" s="423" t="inlineStr">
+        <is>
+          <t>Valuation method for a balance-sheet lender (debt funds earning assets; FCF/DCF not meaningful)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" s="307" t="inlineStr">
+        <is>
+          <t>Cost of Equity (CAPM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" s="307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Risk-free rate</t>
+        </is>
+      </c>
+      <c r="D133" s="344" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" s="307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Beta</t>
+        </is>
+      </c>
+      <c r="D134" s="419" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" s="307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Equity risk premium</t>
+        </is>
+      </c>
+      <c r="D135" s="344" t="n">
+        <v>0.055</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" s="307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Cost of equity (Ke)</t>
+        </is>
+      </c>
+      <c r="D136" s="344">
+        <f>D133+D134*D135</f>
+        <v>0.1005</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" s="307" t="inlineStr">
+        <is>
+          <t>Dividend &amp; Terminal Assumptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" s="307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Payout ratio (explicit period)</t>
+        </is>
+      </c>
+      <c r="D139" s="344" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140" s="307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Terminal growth (g)</t>
+        </is>
+      </c>
+      <c r="D140" s="344" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="B141" s="307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Terminal payout ratio</t>
+        </is>
+      </c>
+      <c r="D141" s="344" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" s="307" t="inlineStr">
+        <is>
+          <t>Adjusted EPS (USD)</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="O143" s="419">
+        <f>O104</f>
+        <v>1.406825459967534</v>
+      </c>
+      <c r="T143" s="419">
+        <f>T104</f>
+        <v>1.5055993169648616</v>
+      </c>
+      <c r="U143" s="419">
+        <f>U104</f>
+        <v>1.677182670974769</v>
+      </c>
+      <c r="V143" s="419">
+        <f>V104</f>
+        <v>1.8493890072937846</v>
+      </c>
+      <c r="W143" s="419">
+        <f>W104</f>
+        <v>2.010285641827722</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="B144" s="307" t="inlineStr">
+        <is>
+          <t>Dividend per share (USD)</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="O144" s="419">
+        <f>$D$139*O143</f>
+        <v>0.4220476379902602</v>
+      </c>
+      <c r="T144" s="419">
+        <f>$D$139*T143</f>
+        <v>0.45167979508945844</v>
+      </c>
+      <c r="U144" s="419">
+        <f>$D$139*U143</f>
+        <v>0.5031548012924307</v>
+      </c>
+      <c r="V144" s="419">
+        <f>$D$139*V143</f>
+        <v>0.5548167021881354</v>
+      </c>
+      <c r="W144" s="419">
+        <f>$D$139*W143</f>
+        <v>0.6030856925483167</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" s="307" t="inlineStr">
+        <is>
+          <t>Discount period (t)</t>
+        </is>
+      </c>
+      <c r="O145" t="n">
+        <v>1</v>
+      </c>
+      <c r="T145" t="n">
+        <v>2</v>
+      </c>
+      <c r="U145" t="n">
+        <v>3</v>
+      </c>
+      <c r="V145" t="n">
+        <v>4</v>
+      </c>
+      <c r="W145" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" s="307" t="inlineStr">
+        <is>
+          <t>Discount factor</t>
+        </is>
+      </c>
+      <c r="O146" s="424">
+        <f>1/(1+$D$136)^O145</f>
+        <v>0.9086778736937755</v>
+      </c>
+      <c r="T146" s="424">
+        <f>1/(1+$D$136)^T145</f>
+        <v>0.825695478140641</v>
+      </c>
+      <c r="U146" s="424">
+        <f>1/(1+$D$136)^U145</f>
+        <v>0.750291211395403</v>
+      </c>
+      <c r="V146" s="424">
+        <f>1/(1+$D$136)^V145</f>
+        <v>0.6817730226219019</v>
+      </c>
+      <c r="W146" s="424">
+        <f>1/(1+$D$136)^W145</f>
+        <v>0.6195120605378481</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="B147" s="307" t="inlineStr">
+        <is>
+          <t>PV of dividend (USD)</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="O147" s="419">
+        <f>O144*O146</f>
+        <v>0.3835053502864699</v>
+      </c>
+      <c r="T147" s="419">
+        <f>T144*T146</f>
+        <v>0.37294996437285716</v>
+      </c>
+      <c r="U147" s="419">
+        <f>U144*U146</f>
+        <v>0.37751262538111113</v>
+      </c>
+      <c r="V147" s="419">
+        <f>V144*V146</f>
+        <v>0.3782590600519206</v>
+      </c>
+      <c r="W147" s="419">
+        <f>W144*W146</f>
+        <v>0.3736188600715028</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="B149" s="307" t="inlineStr">
+        <is>
+          <t>PV of dividends, 2026-2030 (USD)</t>
+        </is>
+      </c>
+      <c r="D149" s="419">
+        <f>O147+T147+U147+V147+W147</f>
+        <v>1.8858458601638617</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="B150" s="307" t="inlineStr">
+        <is>
+          <t>Terminal value at 2030 (USD)</t>
+        </is>
+      </c>
+      <c r="D150" s="419">
+        <f>$D$141*W143*(1+$D$140)/($D$136-$D$140)</f>
+        <v>20.559091457557265</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" s="307" t="inlineStr">
+        <is>
+          <t>PV of terminal value (USD)</t>
+        </is>
+      </c>
+      <c r="D151" s="419">
+        <f>D150*W146</f>
+        <v>12.736605111657372</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="B152" s="82" t="inlineStr">
+        <is>
+          <t>Intrinsic value / share (USD)</t>
+        </is>
+      </c>
+      <c r="D152" s="419">
+        <f>D149+D151</f>
+        <v>14.622450971821234</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" s="307" t="inlineStr">
+        <is>
+          <t>USD/CAD</t>
+        </is>
+      </c>
+      <c r="D153" s="424">
+        <f>O110</f>
+        <v>1.4212</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" s="82" t="inlineStr">
+        <is>
+          <t>Intrinsic value / share (CAD)</t>
+        </is>
+      </c>
+      <c r="D154" s="419">
+        <f>D152*D153</f>
+        <v>20.78142732115234</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="B155" s="307" t="inlineStr">
+        <is>
+          <t>Current share price (CAD)</t>
+        </is>
+      </c>
+      <c r="D155" s="419">
+        <f>O109</f>
+        <v>28.86</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" s="307" t="inlineStr">
+        <is>
+          <t>Upside / (downside)</t>
+        </is>
+      </c>
+      <c r="D156" s="344">
+        <f>D154/D155-1</f>
+        <v>-0.2799228232448947</v>
       </c>
     </row>
   </sheetData>
